--- a/data/hex_xlsx/LUOTEA.HE.xlsx
+++ b/data/hex_xlsx/LUOTEA.HE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="550">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -918,31 +918,34 @@
     <t>Total Tangible Assets, Gross</t>
   </si>
   <si>
+    <t>Tangible assets (not used)</t>
+  </si>
+  <si>
+    <t>Land</t>
+  </si>
+  <si>
+    <t>Land, Gross</t>
+  </si>
+  <si>
+    <t>Acc Depr Land</t>
+  </si>
+  <si>
+    <t>Buildings and constructions</t>
+  </si>
+  <si>
+    <t>Buildings &amp; Constructions, Gross</t>
+  </si>
+  <si>
+    <t>Acc Depr Buildings &amp; Constructions</t>
+  </si>
+  <si>
+    <t>Buildings and constructions - Balancing value</t>
+  </si>
+  <si>
+    <t>Buildings &amp; Constructions, Net - Balancing value</t>
+  </si>
+  <si>
     <t>Tangible assets</t>
-  </si>
-  <si>
-    <t>Land</t>
-  </si>
-  <si>
-    <t>Land, Gross</t>
-  </si>
-  <si>
-    <t>Acc Depr Land</t>
-  </si>
-  <si>
-    <t>Buildings and constructions</t>
-  </si>
-  <si>
-    <t>Buildings &amp; Constructions, Gross</t>
-  </si>
-  <si>
-    <t>Acc Depr Buildings &amp; Constructions</t>
-  </si>
-  <si>
-    <t>Buildings and constructions - Balancing value</t>
-  </si>
-  <si>
-    <t>Buildings &amp; Constructions, Net - Balancing value</t>
   </si>
   <si>
     <t>Machinery &amp; Equipment, Gross</t>
@@ -1791,7 +1794,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1872,6 +1875,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -15467,7 +15473,7 @@
       </c>
     </row>
     <row r="87" ht="15.0" customHeight="1">
-      <c r="A87" s="14" t="s">
+      <c r="A87" s="27" t="s">
         <v>299</v>
       </c>
       <c r="B87" s="19">
@@ -16001,7 +16007,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B96" s="18"/>
       <c r="C96" s="15">
@@ -16070,7 +16076,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B97" s="18"/>
       <c r="C97" s="15">
@@ -16137,7 +16143,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B98" s="18"/>
       <c r="C98" s="22">
@@ -16204,7 +16210,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B99" s="18"/>
       <c r="C99" s="19">
@@ -16235,7 +16241,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B100" s="18"/>
       <c r="C100" s="18"/>
@@ -16276,7 +16282,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B101" s="18"/>
       <c r="C101" s="19">
@@ -16345,7 +16351,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B102" s="18"/>
       <c r="C102" s="19">
@@ -16412,7 +16418,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B103" s="18"/>
       <c r="C103" s="21">
@@ -16479,7 +16485,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B104" s="18"/>
       <c r="C104" s="18"/>
@@ -16512,7 +16518,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B105" s="18"/>
       <c r="C105" s="18"/>
@@ -16543,7 +16549,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B106" s="18"/>
       <c r="C106" s="19">
@@ -16612,7 +16618,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B107" s="18"/>
       <c r="C107" s="19">
@@ -16679,7 +16685,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B108" s="18"/>
       <c r="C108" s="18"/>
@@ -16710,7 +16716,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B109" s="18"/>
       <c r="C109" s="18"/>
@@ -16745,7 +16751,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B110" s="15">
         <v>172.48</v>
@@ -16786,7 +16792,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B111" s="18"/>
       <c r="C111" s="15">
@@ -16825,7 +16831,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B112" s="18"/>
       <c r="C112" s="22">
@@ -16864,7 +16870,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B113" s="18"/>
       <c r="C113" s="21">
@@ -16895,7 +16901,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B114" s="18"/>
       <c r="C114" s="15">
@@ -16958,7 +16964,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B115" s="18"/>
       <c r="C115" s="18"/>
@@ -17015,7 +17021,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B116" s="18"/>
       <c r="C116" s="18"/>
@@ -17070,7 +17076,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B117" s="18"/>
       <c r="C117" s="21">
@@ -17109,7 +17115,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B118" s="18">
         <v>0.0</v>
@@ -17146,7 +17152,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B119" s="19">
         <v>1.18</v>
@@ -17183,7 +17189,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B120" s="19">
         <v>24.81</v>
@@ -17254,7 +17260,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B121" s="19">
         <v>4.73</v>
@@ -17325,7 +17331,7 @@
     </row>
     <row r="122" ht="15.0" customHeight="1">
       <c r="A122" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B122" s="18"/>
       <c r="C122" s="19">
@@ -17362,7 +17368,7 @@
     </row>
     <row r="123" ht="15.0" customHeight="1">
       <c r="A123" s="16" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B123" s="17">
         <v>792.72</v>
@@ -17433,7 +17439,7 @@
     </row>
     <row r="124" ht="15.0" customHeight="1">
       <c r="A124" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B124" s="18"/>
       <c r="C124" s="18"/>
@@ -17476,7 +17482,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="16" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B125" s="17">
         <v>1677.59</v>
@@ -17547,7 +17553,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B126" s="18"/>
       <c r="C126" s="15">
@@ -17600,7 +17606,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B127" s="18"/>
       <c r="C127" s="18"/>
@@ -17661,7 +17667,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B128" s="18"/>
       <c r="C128" s="18"/>
@@ -17708,7 +17714,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B129" s="18"/>
       <c r="C129" s="18"/>
@@ -17747,7 +17753,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B130" s="18"/>
       <c r="C130" s="18"/>
@@ -17782,7 +17788,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B131" s="18">
         <v>0.0</v>
@@ -17851,7 +17857,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B132" s="19">
         <v>70.88</v>
@@ -17912,7 +17918,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B133" s="15">
         <v>870.69</v>
@@ -17983,7 +17989,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B134" s="18"/>
       <c r="C134" s="15">
@@ -18050,7 +18056,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B135" s="18"/>
       <c r="C135" s="15">
@@ -18103,7 +18109,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B136" s="18"/>
       <c r="C136" s="15">
@@ -18170,7 +18176,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B137" s="18"/>
       <c r="C137" s="18"/>
@@ -18203,7 +18209,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B138" s="18"/>
       <c r="C138" s="15">
@@ -18270,7 +18276,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B139" s="18"/>
       <c r="C139" s="15">
@@ -18323,7 +18329,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B140" s="18"/>
       <c r="C140" s="18"/>
@@ -18358,7 +18364,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B141" s="18"/>
       <c r="C141" s="19">
@@ -18411,7 +18417,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B142" s="18"/>
       <c r="C142" s="18"/>
@@ -18440,7 +18446,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B143" s="18"/>
       <c r="C143" s="18"/>
@@ -18477,7 +18483,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B144" s="18"/>
       <c r="C144" s="18"/>
@@ -18526,7 +18532,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B145" s="19">
         <v>2.36</v>
@@ -18591,7 +18597,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B146" s="19">
         <v>21.27</v>
@@ -18662,7 +18668,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B147" s="21">
         <v>-1.18</v>
@@ -18705,7 +18711,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B148" s="17">
         <v>964.02</v>
@@ -18776,7 +18782,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B149" s="18"/>
       <c r="C149" s="15">
@@ -18831,7 +18837,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B150" s="18"/>
       <c r="C150" s="15">
@@ -18874,7 +18880,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B151" s="18"/>
       <c r="C151" s="18"/>
@@ -18903,7 +18909,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B152" s="19">
         <v>59.07</v>
@@ -18966,7 +18972,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B153" s="15">
         <v>103.96</v>
@@ -19027,7 +19033,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B154" s="18">
         <v>0.0</v>
@@ -19098,7 +19104,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B155" s="18"/>
       <c r="C155" s="19">
@@ -19151,7 +19157,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B156" s="18"/>
       <c r="C156" s="19">
@@ -19186,7 +19192,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B157" s="18"/>
       <c r="C157" s="18">
@@ -19239,7 +19245,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B158" s="18"/>
       <c r="C158" s="18"/>
@@ -19272,7 +19278,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B159" s="18"/>
       <c r="C159" s="18"/>
@@ -19301,7 +19307,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B160" s="19">
         <v>10.63</v>
@@ -19372,7 +19378,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B161" s="18">
         <v>0.0</v>
@@ -19443,7 +19449,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B162" s="19">
         <v>53.16</v>
@@ -19514,7 +19520,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B163" s="18"/>
       <c r="C163" s="18"/>
@@ -19555,7 +19561,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="16" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B164" s="17">
         <v>226.83</v>
@@ -19626,7 +19632,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B165" s="18"/>
       <c r="C165" s="18"/>
@@ -19657,7 +19663,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B166" s="19">
         <v>1.18</v>
@@ -19704,7 +19710,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="16" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B167" s="17">
         <v>1192.03</v>
@@ -19775,7 +19781,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B168" s="19">
         <v>11.81</v>
@@ -19846,7 +19852,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B169" s="18"/>
       <c r="C169" s="22">
@@ -19913,7 +19919,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B170" s="18"/>
       <c r="C170" s="18"/>
@@ -19948,7 +19954,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B171" s="18"/>
       <c r="C171" s="18">
@@ -20003,7 +20009,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B172" s="18"/>
       <c r="C172" s="18"/>
@@ -20034,7 +20040,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B173" s="18"/>
       <c r="C173" s="18"/>
@@ -20136,7 +20142,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B175" s="19">
         <v>1.18</v>
@@ -20193,7 +20199,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B176" s="15">
         <v>609.6</v>
@@ -20264,7 +20270,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B177" s="18"/>
       <c r="C177" s="18"/>
@@ -20321,7 +20327,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B178" s="18"/>
       <c r="C178" s="18"/>
@@ -20358,7 +20364,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="16" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B179" s="17">
         <v>485.56</v>
@@ -20490,7 +20496,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="16" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B181" s="20"/>
       <c r="C181" s="20"/>
@@ -20551,7 +20557,7 @@
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B182" s="18"/>
       <c r="C182" s="18"/>
@@ -20584,7 +20590,7 @@
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="16" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B183" s="17">
         <v>485.56</v>
@@ -20655,7 +20661,7 @@
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B184" s="18"/>
       <c r="C184" s="18"/>
@@ -20694,7 +20700,7 @@
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="16" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B185" s="17">
         <v>1677.59</v>
@@ -20765,7 +20771,7 @@
     </row>
     <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B186" s="19">
         <v>38.21</v>
@@ -20836,7 +20842,7 @@
     </row>
     <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B187" s="19">
         <v>0.59</v>
@@ -20907,7 +20913,7 @@
     </row>
     <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B188" s="19">
         <v>38.8</v>
@@ -20978,7 +20984,7 @@
     </row>
     <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B189" s="18"/>
       <c r="C189" s="15">
@@ -21043,7 +21049,7 @@
     </row>
     <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B190" s="18"/>
       <c r="C190" s="19">
@@ -21108,7 +21114,7 @@
     </row>
     <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B191" s="18"/>
       <c r="C191" s="15">
@@ -21173,7 +21179,7 @@
     </row>
     <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B192" s="18"/>
       <c r="C192" s="19">
@@ -21238,7 +21244,7 @@
     </row>
     <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B193" s="18"/>
       <c r="C193" s="15">
@@ -21303,7 +21309,7 @@
     </row>
     <row r="194" ht="15.0" customHeight="1">
       <c r="A194" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B194" s="18"/>
       <c r="C194" s="18">
@@ -21366,7 +21372,7 @@
     </row>
     <row r="195" ht="15.0" customHeight="1">
       <c r="A195" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B195" s="18"/>
       <c r="C195" s="18">
@@ -21425,7 +21431,7 @@
     </row>
     <row r="196" ht="15.0" customHeight="1">
       <c r="A196" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B196" s="18"/>
       <c r="C196" s="18"/>
@@ -21462,7 +21468,7 @@
     </row>
     <row r="197" ht="15.0" customHeight="1">
       <c r="A197" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B197" s="18"/>
       <c r="C197" s="18"/>
@@ -21503,7 +21509,7 @@
     </row>
     <row r="198" ht="15.0" customHeight="1">
       <c r="A198" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B198" s="18"/>
       <c r="C198" s="18"/>
@@ -21565,7 +21571,7 @@
     </row>
     <row r="200" ht="15.0" customHeight="1">
       <c r="A200" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B200" s="18"/>
       <c r="C200" s="18"/>
@@ -21645,7 +21651,7 @@
     </row>
     <row r="202" ht="15.0" customHeight="1">
       <c r="A202" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B202" s="18"/>
       <c r="C202" s="18"/>
@@ -21686,7 +21692,7 @@
     </row>
     <row r="203" ht="15.0" customHeight="1">
       <c r="A203" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B203" s="18"/>
       <c r="C203" s="18"/>
@@ -21727,7 +21733,7 @@
     </row>
     <row r="204" ht="15.0" customHeight="1">
       <c r="A204" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B204" s="18"/>
       <c r="C204" s="18"/>
@@ -21762,7 +21768,7 @@
     </row>
     <row r="205" ht="15.0" customHeight="1">
       <c r="A205" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B205" s="18"/>
       <c r="C205" s="18"/>
@@ -21791,7 +21797,7 @@
     </row>
     <row r="206" ht="15.0" customHeight="1">
       <c r="A206" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B206" s="18"/>
       <c r="C206" s="18"/>
@@ -21826,7 +21832,7 @@
     </row>
     <row r="207" ht="15.0" customHeight="1">
       <c r="A207" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B207" s="18"/>
       <c r="C207" s="18"/>
@@ -21863,7 +21869,7 @@
     </row>
     <row r="208" ht="15.0" customHeight="1">
       <c r="A208" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B208" s="18"/>
       <c r="C208" s="15">
@@ -21918,7 +21924,7 @@
     </row>
     <row r="209" ht="15.0" customHeight="1">
       <c r="A209" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B209" s="18"/>
       <c r="C209" s="15">
@@ -21973,7 +21979,7 @@
     </row>
     <row r="210" ht="15.0" customHeight="1">
       <c r="A210" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B210" s="18"/>
       <c r="C210" s="15">
@@ -22028,7 +22034,7 @@
     </row>
     <row r="211" ht="15.0" customHeight="1">
       <c r="A211" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B211" s="18"/>
       <c r="C211" s="19">
@@ -22083,7 +22089,7 @@
     </row>
     <row r="212" ht="15.0" customHeight="1">
       <c r="A212" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B212" s="18"/>
       <c r="C212" s="19">
@@ -22136,7 +22142,7 @@
     </row>
     <row r="213" ht="15.0" customHeight="1">
       <c r="A213" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B213" s="18"/>
       <c r="C213" s="19">
@@ -22187,7 +22193,7 @@
     </row>
     <row r="214" ht="15.0" customHeight="1">
       <c r="A214" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B214" s="18"/>
       <c r="C214" s="15">
@@ -22238,7 +22244,7 @@
     </row>
     <row r="215" ht="15.0" customHeight="1">
       <c r="A215" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B215" s="18"/>
       <c r="C215" s="18"/>
@@ -22269,7 +22275,7 @@
     </row>
     <row r="216" ht="15.0" customHeight="1">
       <c r="A216" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B216" s="18"/>
       <c r="C216" s="18"/>
@@ -22300,7 +22306,7 @@
     </row>
     <row r="217" ht="15.0" customHeight="1">
       <c r="A217" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B217" s="18"/>
       <c r="C217" s="18"/>
@@ -22335,7 +22341,7 @@
     </row>
     <row r="218" ht="15.0" customHeight="1">
       <c r="A218" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B218" s="18"/>
       <c r="C218" s="18"/>
@@ -22364,7 +22370,7 @@
     </row>
     <row r="219" ht="15.0" customHeight="1">
       <c r="A219" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B219" s="18"/>
       <c r="C219" s="18"/>
@@ -22399,7 +22405,7 @@
     </row>
     <row r="220" ht="15.0" customHeight="1">
       <c r="A220" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B220" s="19">
         <v>38.21</v>
@@ -22470,7 +22476,7 @@
     </row>
     <row r="221" ht="15.0" customHeight="1">
       <c r="A221" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B221" s="19">
         <v>0.59</v>
@@ -22541,7 +22547,7 @@
     </row>
     <row r="222" ht="15.0" customHeight="1">
       <c r="A222" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B222" s="19">
         <v>38.8</v>
@@ -22612,7 +22618,7 @@
     </row>
     <row r="223" ht="15.0" customHeight="1">
       <c r="A223" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B223" s="19">
         <v>1.0</v>
@@ -23479,7 +23485,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23865,70 +23871,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -24004,7 +24010,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -24102,7 +24108,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B20" s="21">
         <v>-7.02</v>
@@ -24137,7 +24143,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B21" s="21">
         <v>-22.23</v>
@@ -24174,7 +24180,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -24211,7 +24217,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -24244,7 +24250,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B24" s="21">
         <v>-44.47</v>
@@ -24275,7 +24281,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B25" s="22">
         <v>-1565.8</v>
@@ -24304,7 +24310,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B26" s="15">
         <v>1069.62</v>
@@ -24430,7 +24436,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -24546,7 +24552,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B30" s="15">
         <v>623.75</v>
@@ -24680,7 +24686,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
@@ -24725,7 +24731,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B33" s="18"/>
       <c r="C33" s="18"/>
@@ -24756,7 +24762,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
@@ -24811,7 +24817,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B35" s="19">
         <v>10.53</v>
@@ -24878,7 +24884,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
@@ -24909,7 +24915,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B37" s="18"/>
       <c r="C37" s="18"/>
@@ -24938,7 +24944,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B38" s="21">
         <v>-55.0</v>
@@ -24993,7 +24999,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B39" s="22">
         <v>-148.62</v>
@@ -25135,7 +25141,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B41" s="19">
         <v>95.96</v>
@@ -25206,7 +25212,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B42" s="18"/>
       <c r="C42" s="18"/>
@@ -25239,7 +25245,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B43" s="18"/>
       <c r="C43" s="18"/>
@@ -25272,7 +25278,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B44" s="22">
         <v>-124.05</v>
@@ -25343,7 +25349,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B45" s="19">
         <v>7.02</v>
@@ -25414,7 +25420,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B46" s="21">
         <v>-12.87</v>
@@ -25485,7 +25491,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B47" s="19">
         <v>1.17</v>
@@ -25528,7 +25534,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="16" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B48" s="17">
         <v>884.71</v>
@@ -25599,7 +25605,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B49" s="22">
         <v>-129.9</v>
@@ -25670,7 +25676,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
@@ -25717,7 +25723,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
@@ -25748,7 +25754,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B52" s="22">
         <v>-273.84</v>
@@ -25819,7 +25825,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
@@ -25868,7 +25874,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B54" s="19">
         <v>17.55</v>
@@ -25917,7 +25923,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B55" s="18"/>
       <c r="C55" s="18"/>
@@ -25970,7 +25976,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
@@ -26035,7 +26041,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B57" s="19">
         <v>18.72</v>
@@ -26092,7 +26098,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
@@ -26123,7 +26129,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
@@ -26164,7 +26170,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
@@ -26197,7 +26203,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
@@ -26228,7 +26234,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
@@ -26263,7 +26269,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="16" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B63" s="25">
         <v>-367.46</v>
@@ -26334,7 +26340,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B64" s="15">
         <v>351.08</v>
@@ -26399,7 +26405,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B65" s="22">
         <v>-351.08</v>
@@ -26436,7 +26442,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B66" s="15">
         <v>643.64</v>
@@ -26507,7 +26513,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
@@ -26536,7 +26542,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B68" s="22">
         <v>-478.64</v>
@@ -26605,7 +26611,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B69" s="22">
         <v>-223.52</v>
@@ -26676,7 +26682,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B70" s="22">
         <v>-236.39</v>
@@ -26719,7 +26725,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B71" s="18"/>
       <c r="C71" s="18"/>
@@ -26766,7 +26772,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B72" s="18"/>
       <c r="C72" s="18"/>
@@ -26795,7 +26801,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B73" s="18"/>
       <c r="C73" s="18"/>
@@ -26824,7 +26830,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B74" s="18"/>
       <c r="C74" s="18"/>
@@ -26863,7 +26869,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B75" s="18"/>
       <c r="C75" s="18"/>
@@ -26894,7 +26900,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
@@ -26927,7 +26933,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="16" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B77" s="25">
         <v>-294.9</v>
@@ -26998,7 +27004,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B78" s="19">
         <v>1.17</v>
@@ -27069,7 +27075,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B79" s="15">
         <v>400.49</v>
@@ -27140,7 +27146,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B80" s="15">
         <v>185.48</v>
@@ -27211,7 +27217,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B81" s="15">
         <v>222.35</v>
@@ -27266,7 +27272,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B82" s="22">
         <v>-437.68</v>
@@ -27295,7 +27301,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B83" s="25">
         <v>-214.16</v>
@@ -27366,7 +27372,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B84" s="18"/>
       <c r="C84" s="18"/>
@@ -27395,7 +27401,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B85" s="18"/>
       <c r="C85" s="18"/>
@@ -28358,7 +28364,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -28530,28 +28536,28 @@
         <v>39</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -29012,7 +29018,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -29112,3721 +29118,3721 @@
         <v>71</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="27" t="s">
-        <v>498</v>
-      </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="28"/>
-      <c r="X20" s="28"/>
-      <c r="Y20" s="28"/>
-      <c r="Z20" s="28"/>
-      <c r="AA20" s="28"/>
-      <c r="AB20" s="28"/>
-      <c r="AC20" s="28"/>
-      <c r="AD20" s="28"/>
+      <c r="A20" s="28" t="s">
+        <v>499</v>
+      </c>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="29"/>
+      <c r="X20" s="29"/>
+      <c r="Y20" s="29"/>
+      <c r="Z20" s="29"/>
+      <c r="AA20" s="29"/>
+      <c r="AB20" s="29"/>
+      <c r="AC20" s="29"/>
+      <c r="AD20" s="29"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="29" t="s">
-        <v>498</v>
-      </c>
-      <c r="B21" s="30">
+      <c r="A21" s="30" t="s">
+        <v>499</v>
+      </c>
+      <c r="B21" s="31">
         <v>2619.09</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <v>2768.78</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <v>2741.32</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <v>6893.47</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <v>7551.35</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="31">
         <v>7345.95</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="31">
         <v>6721.68</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="31">
         <v>8060.28</v>
       </c>
-      <c r="J21" s="30">
+      <c r="J21" s="31">
         <v>7117.34</v>
       </c>
-      <c r="K21" s="30">
+      <c r="K21" s="31">
         <v>7152.36</v>
       </c>
-      <c r="L21" s="30">
+      <c r="L21" s="31">
         <v>5781.41</v>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="31">
         <v>5465.76</v>
       </c>
-      <c r="N21" s="30">
+      <c r="N21" s="31">
         <v>3738.38</v>
       </c>
-      <c r="O21" s="30">
+      <c r="O21" s="31">
         <v>4092.07</v>
       </c>
-      <c r="P21" s="30">
+      <c r="P21" s="31">
         <v>4884.9</v>
       </c>
-      <c r="Q21" s="30">
+      <c r="Q21" s="31">
         <v>5600.34</v>
       </c>
-      <c r="R21" s="30">
+      <c r="R21" s="31">
         <v>4903.2</v>
       </c>
-      <c r="S21" s="30">
+      <c r="S21" s="31">
         <v>6972.7</v>
       </c>
-      <c r="T21" s="30">
+      <c r="T21" s="31">
         <v>6485.29</v>
       </c>
-      <c r="U21" s="30">
+      <c r="U21" s="31">
         <v>4739.53</v>
       </c>
-      <c r="V21" s="30">
+      <c r="V21" s="31">
         <v>4233.66</v>
       </c>
-      <c r="W21" s="30">
+      <c r="W21" s="31">
         <v>3950.29</v>
       </c>
-      <c r="X21" s="30">
+      <c r="X21" s="31">
         <v>2145.43</v>
       </c>
-      <c r="Y21" s="30">
+      <c r="Y21" s="31">
         <v>2620.4</v>
       </c>
-      <c r="Z21" s="30">
+      <c r="Z21" s="31">
         <v>3184.73</v>
       </c>
-      <c r="AA21" s="30">
+      <c r="AA21" s="31">
         <v>3090.02</v>
       </c>
-      <c r="AB21" s="30">
+      <c r="AB21" s="31">
         <v>1068.16</v>
       </c>
-      <c r="AC21" s="30">
+      <c r="AC21" s="31">
         <v>917.89</v>
       </c>
-      <c r="AD21" s="30">
+      <c r="AD21" s="31">
         <v>144.45</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="29" t="s">
-        <v>499</v>
-      </c>
-      <c r="B22" s="30">
+      <c r="A22" s="30" t="s">
+        <v>500</v>
+      </c>
+      <c r="B22" s="31">
         <v>5038.52</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <v>5961.35</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="31">
         <v>6491.36</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <v>7314.39</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="31">
         <v>7853.54</v>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="31">
         <v>7424.74</v>
       </c>
-      <c r="H22" s="30">
+      <c r="H22" s="31">
         <v>7263.57</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="31">
         <v>7172.6</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="31">
         <v>6053.41</v>
       </c>
-      <c r="K22" s="30">
+      <c r="K22" s="31">
         <v>5910.57</v>
       </c>
-      <c r="L22" s="30">
+      <c r="L22" s="31">
         <v>5352.15</v>
       </c>
-      <c r="M22" s="30">
+      <c r="M22" s="31">
         <v>4996.61</v>
       </c>
-      <c r="N22" s="30">
+      <c r="N22" s="31">
         <v>4177.53</v>
       </c>
-      <c r="O22" s="30">
+      <c r="O22" s="31">
         <v>4976.09</v>
       </c>
-      <c r="P22" s="30">
+      <c r="P22" s="31">
         <v>5413.31</v>
       </c>
-      <c r="Q22" s="30">
+      <c r="Q22" s="31">
         <v>5709.21</v>
       </c>
-      <c r="R22" s="30">
+      <c r="R22" s="31">
         <v>6369.57</v>
       </c>
-      <c r="S22" s="30">
+      <c r="S22" s="31">
         <v>5147.41</v>
       </c>
-      <c r="T22" s="30">
+      <c r="T22" s="31">
         <v>4378.31</v>
       </c>
-      <c r="U22" s="30">
+      <c r="U22" s="31">
         <v>3516.51</v>
       </c>
-      <c r="V22" s="30">
+      <c r="V22" s="31">
         <v>3285.29</v>
       </c>
-      <c r="W22" s="30">
+      <c r="W22" s="31">
         <v>3127.5</v>
       </c>
-      <c r="X22" s="30">
+      <c r="X22" s="31">
         <v>2198.77</v>
       </c>
-      <c r="Y22" s="30">
+      <c r="Y22" s="31">
         <v>2118.91</v>
       </c>
-      <c r="Z22" s="30">
+      <c r="Z22" s="31">
         <v>1683.66</v>
       </c>
-      <c r="AA22" s="31"/>
-      <c r="AB22" s="31"/>
-      <c r="AC22" s="31"/>
-      <c r="AD22" s="31"/>
+      <c r="AA22" s="32"/>
+      <c r="AB22" s="32"/>
+      <c r="AC22" s="32"/>
+      <c r="AD22" s="32"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="27" t="s">
-        <v>500</v>
-      </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
-      <c r="V23" s="28"/>
-      <c r="W23" s="28"/>
-      <c r="X23" s="28"/>
-      <c r="Y23" s="28"/>
-      <c r="Z23" s="28"/>
-      <c r="AA23" s="28"/>
-      <c r="AB23" s="28"/>
-      <c r="AC23" s="28"/>
-      <c r="AD23" s="28"/>
+      <c r="A23" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="29"/>
+      <c r="X23" s="29"/>
+      <c r="Y23" s="29"/>
+      <c r="Z23" s="29"/>
+      <c r="AA23" s="29"/>
+      <c r="AB23" s="29"/>
+      <c r="AC23" s="29"/>
+      <c r="AD23" s="29"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="29" t="s">
-        <v>500</v>
-      </c>
-      <c r="B24" s="30">
+      <c r="A24" s="30" t="s">
+        <v>501</v>
+      </c>
+      <c r="B24" s="31">
         <v>818.75</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <v>969.11</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <v>986.26</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <v>5220.56</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="31">
         <v>6121.35</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="31">
         <v>6009.59</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="31">
         <v>5750.72</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="31">
         <v>6898.56</v>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="31">
         <v>6764.12</v>
       </c>
-      <c r="K24" s="30">
+      <c r="K24" s="31">
         <v>6749.16</v>
       </c>
-      <c r="L24" s="30">
+      <c r="L24" s="31">
         <v>5309.58</v>
       </c>
-      <c r="M24" s="30">
+      <c r="M24" s="31">
         <v>4927.04</v>
       </c>
-      <c r="N24" s="30">
+      <c r="N24" s="31">
         <v>3131.61</v>
       </c>
-      <c r="O24" s="30">
+      <c r="O24" s="31">
         <v>3106.14</v>
       </c>
-      <c r="P24" s="30">
+      <c r="P24" s="31">
         <v>4008.35</v>
       </c>
-      <c r="Q24" s="30">
+      <c r="Q24" s="31">
         <v>4633.92</v>
       </c>
-      <c r="R24" s="30">
+      <c r="R24" s="31">
         <v>3731.42</v>
       </c>
-      <c r="S24" s="30">
+      <c r="S24" s="31">
         <v>6286.5</v>
       </c>
-      <c r="T24" s="30">
+      <c r="T24" s="31">
         <v>6181.39</v>
       </c>
-      <c r="U24" s="30">
+      <c r="U24" s="31">
         <v>4111.8</v>
       </c>
-      <c r="V24" s="30">
+      <c r="V24" s="31">
         <v>3714.87</v>
       </c>
-      <c r="W24" s="30">
+      <c r="W24" s="31">
         <v>3290.1</v>
       </c>
-      <c r="X24" s="30">
+      <c r="X24" s="31">
         <v>1606.58</v>
       </c>
-      <c r="Y24" s="30">
+      <c r="Y24" s="31">
         <v>2043.56</v>
       </c>
-      <c r="Z24" s="30">
+      <c r="Z24" s="31">
         <v>2190.17</v>
       </c>
-      <c r="AA24" s="30">
+      <c r="AA24" s="31">
         <v>2818.46</v>
       </c>
-      <c r="AB24" s="30">
+      <c r="AB24" s="31">
         <v>1051.23</v>
       </c>
-      <c r="AC24" s="30">
+      <c r="AC24" s="31">
         <v>917.3</v>
       </c>
-      <c r="AD24" s="30">
+      <c r="AD24" s="31">
         <v>131.89</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="29" t="s">
-        <v>501</v>
-      </c>
-      <c r="B25" s="30">
+      <c r="A25" s="30" t="s">
+        <v>502</v>
+      </c>
+      <c r="B25" s="31">
         <v>3191.34</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <v>4244.0</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="31">
         <v>5013.5</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="31">
         <v>6002.09</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="31">
         <v>6748.93</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="31">
         <v>6573.14</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="31">
         <v>6571.82</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="31">
         <v>6550.96</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J25" s="31">
         <v>5544.23</v>
       </c>
-      <c r="K25" s="30">
+      <c r="K25" s="31">
         <v>5202.25</v>
       </c>
-      <c r="L25" s="30">
+      <c r="L25" s="31">
         <v>4557.69</v>
       </c>
-      <c r="M25" s="30">
+      <c r="M25" s="31">
         <v>4156.48</v>
       </c>
-      <c r="N25" s="30">
+      <c r="N25" s="31">
         <v>3355.64</v>
       </c>
-      <c r="O25" s="30">
+      <c r="O25" s="31">
         <v>4103.76</v>
       </c>
-      <c r="P25" s="30">
+      <c r="P25" s="31">
         <v>4676.15</v>
       </c>
-      <c r="Q25" s="30">
+      <c r="Q25" s="31">
         <v>4980.45</v>
       </c>
-      <c r="R25" s="30">
+      <c r="R25" s="31">
         <v>5620.5</v>
       </c>
-      <c r="S25" s="30">
+      <c r="S25" s="31">
         <v>4602.32</v>
       </c>
-      <c r="T25" s="30">
+      <c r="T25" s="31">
         <v>3833.34</v>
       </c>
-      <c r="U25" s="30">
+      <c r="U25" s="31">
         <v>2930.84</v>
       </c>
-      <c r="V25" s="30">
+      <c r="V25" s="31">
         <v>2612.21</v>
       </c>
-      <c r="W25" s="30">
+      <c r="W25" s="31">
         <v>2490.91</v>
       </c>
-      <c r="X25" s="30">
+      <c r="X25" s="31">
         <v>1758.89</v>
       </c>
-      <c r="Y25" s="30">
+      <c r="Y25" s="31">
         <v>1755.03</v>
       </c>
-      <c r="Z25" s="30">
+      <c r="Z25" s="31">
         <v>1423.34</v>
       </c>
-      <c r="AA25" s="31"/>
-      <c r="AB25" s="31"/>
-      <c r="AC25" s="31"/>
-      <c r="AD25" s="31"/>
+      <c r="AA25" s="32"/>
+      <c r="AB25" s="32"/>
+      <c r="AC25" s="32"/>
+      <c r="AD25" s="32"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="27" t="s">
-        <v>502</v>
-      </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
-      <c r="U26" s="28"/>
-      <c r="V26" s="28"/>
-      <c r="W26" s="28"/>
-      <c r="X26" s="28"/>
-      <c r="Y26" s="28"/>
-      <c r="Z26" s="28"/>
-      <c r="AA26" s="28"/>
-      <c r="AB26" s="28"/>
-      <c r="AC26" s="28"/>
-      <c r="AD26" s="28"/>
+      <c r="A26" s="28" t="s">
+        <v>503</v>
+      </c>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+      <c r="W26" s="29"/>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="29"/>
+      <c r="Z26" s="29"/>
+      <c r="AA26" s="29"/>
+      <c r="AB26" s="29"/>
+      <c r="AC26" s="29"/>
+      <c r="AD26" s="29"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="29" t="s">
-        <v>503</v>
-      </c>
-      <c r="B27" s="32">
+      <c r="A27" s="30" t="s">
+        <v>504</v>
+      </c>
+      <c r="B27" s="33">
         <v>21.1</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <v>24.98</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="33">
         <v>25.42</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <v>134.55</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>157.77</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27" s="31">
         <v>154.89</v>
       </c>
-      <c r="H27" s="30">
+      <c r="H27" s="31">
         <v>148.22</v>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="31">
         <v>177.8</v>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="31">
         <v>174.34</v>
       </c>
-      <c r="K27" s="30">
+      <c r="K27" s="31">
         <v>173.95</v>
       </c>
-      <c r="L27" s="30">
+      <c r="L27" s="31">
         <v>136.85</v>
       </c>
-      <c r="M27" s="30">
+      <c r="M27" s="31">
         <v>126.99</v>
       </c>
-      <c r="N27" s="32">
+      <c r="N27" s="33">
         <v>80.71</v>
       </c>
-      <c r="O27" s="32">
+      <c r="O27" s="33">
         <v>80.06</v>
       </c>
-      <c r="P27" s="30">
+      <c r="P27" s="31">
         <v>103.31</v>
       </c>
-      <c r="Q27" s="30">
+      <c r="Q27" s="31">
         <v>119.43</v>
       </c>
-      <c r="R27" s="32">
+      <c r="R27" s="33">
         <v>96.17</v>
       </c>
-      <c r="S27" s="30">
+      <c r="S27" s="31">
         <v>162.09</v>
       </c>
-      <c r="T27" s="30">
+      <c r="T27" s="31">
         <v>160.44</v>
       </c>
-      <c r="U27" s="30">
+      <c r="U27" s="31">
         <v>107.14</v>
       </c>
-      <c r="V27" s="32">
+      <c r="V27" s="33">
         <v>97.41</v>
       </c>
-      <c r="W27" s="32">
+      <c r="W27" s="33">
         <v>81.55</v>
       </c>
-      <c r="X27" s="32">
+      <c r="X27" s="33">
         <v>39.82</v>
       </c>
-      <c r="Y27" s="32">
+      <c r="Y27" s="33">
         <v>50.65</v>
       </c>
-      <c r="Z27" s="32">
+      <c r="Z27" s="33">
         <v>54.29</v>
       </c>
-      <c r="AA27" s="32">
+      <c r="AA27" s="33">
         <v>69.86</v>
       </c>
-      <c r="AB27" s="32">
+      <c r="AB27" s="33">
         <v>66.42</v>
       </c>
-      <c r="AC27" s="32">
+      <c r="AC27" s="33">
         <v>60.88</v>
       </c>
-      <c r="AD27" s="32">
+      <c r="AD27" s="33">
         <v>35.01</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="29" t="s">
-        <v>504</v>
-      </c>
-      <c r="B28" s="32">
+      <c r="A28" s="30" t="s">
+        <v>505</v>
+      </c>
+      <c r="B28" s="33">
         <v>30.47</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <v>32.97</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="33">
         <v>33.37</v>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="31">
         <v>154.7</v>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="31">
         <v>173.95</v>
       </c>
-      <c r="G28" s="30">
+      <c r="G28" s="31">
         <v>169.42</v>
       </c>
-      <c r="H28" s="30">
+      <c r="H28" s="31">
         <v>169.38</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="31">
         <v>168.84</v>
       </c>
-      <c r="J28" s="30">
+      <c r="J28" s="31">
         <v>142.9</v>
       </c>
-      <c r="K28" s="30">
+      <c r="K28" s="31">
         <v>134.08</v>
       </c>
-      <c r="L28" s="30">
+      <c r="L28" s="31">
         <v>117.47</v>
       </c>
-      <c r="M28" s="30">
+      <c r="M28" s="31">
         <v>107.13</v>
       </c>
-      <c r="N28" s="32">
+      <c r="N28" s="33">
         <v>86.49</v>
       </c>
-      <c r="O28" s="30">
+      <c r="O28" s="31">
         <v>105.78</v>
       </c>
-      <c r="P28" s="30">
+      <c r="P28" s="31">
         <v>120.75</v>
       </c>
-      <c r="Q28" s="30">
+      <c r="Q28" s="31">
         <v>128.85</v>
       </c>
-      <c r="R28" s="30">
+      <c r="R28" s="31">
         <v>145.82</v>
       </c>
-      <c r="S28" s="30">
+      <c r="S28" s="31">
         <v>118.79</v>
       </c>
-      <c r="T28" s="32">
+      <c r="T28" s="33">
         <v>98.6</v>
       </c>
-      <c r="U28" s="32">
+      <c r="U28" s="33">
         <v>74.72</v>
       </c>
-      <c r="V28" s="32">
+      <c r="V28" s="33">
         <v>65.81</v>
       </c>
-      <c r="W28" s="32">
+      <c r="W28" s="33">
         <v>61.74</v>
       </c>
-      <c r="X28" s="32">
+      <c r="X28" s="33">
         <v>50.16</v>
       </c>
-      <c r="Y28" s="32">
+      <c r="Y28" s="33">
         <v>58.19</v>
       </c>
-      <c r="Z28" s="32">
+      <c r="Z28" s="33">
         <v>57.02</v>
       </c>
-      <c r="AA28" s="31"/>
-      <c r="AB28" s="31"/>
-      <c r="AC28" s="31"/>
-      <c r="AD28" s="31"/>
+      <c r="AA28" s="32"/>
+      <c r="AB28" s="32"/>
+      <c r="AC28" s="32"/>
+      <c r="AD28" s="32"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="27" t="s">
-        <v>505</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
-      <c r="U29" s="28"/>
-      <c r="V29" s="28"/>
-      <c r="W29" s="28"/>
-      <c r="X29" s="28"/>
-      <c r="Y29" s="28"/>
-      <c r="Z29" s="28"/>
-      <c r="AA29" s="28"/>
-      <c r="AB29" s="28"/>
-      <c r="AC29" s="28"/>
-      <c r="AD29" s="28"/>
+      <c r="A29" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="29"/>
+      <c r="Y29" s="29"/>
+      <c r="Z29" s="29"/>
+      <c r="AA29" s="29"/>
+      <c r="AB29" s="29"/>
+      <c r="AC29" s="29"/>
+      <c r="AD29" s="29"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>506</v>
-      </c>
-      <c r="B30" s="33">
+      <c r="A30" s="30" t="s">
+        <v>507</v>
+      </c>
+      <c r="B30" s="34">
         <v>59.17</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="34">
         <v>56.76</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="34">
         <v>41.12</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="34">
         <v>4.55</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="34">
         <v>6.62</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="34">
         <v>9.41</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="34">
         <v>10.64</v>
       </c>
-      <c r="I30" s="33">
+      <c r="I30" s="34">
         <v>5.23</v>
       </c>
-      <c r="J30" s="33">
+      <c r="J30" s="34">
         <v>5.77</v>
       </c>
-      <c r="K30" s="33">
+      <c r="K30" s="34">
         <v>7.51</v>
       </c>
-      <c r="L30" s="33">
+      <c r="L30" s="34">
         <v>7.76</v>
       </c>
-      <c r="M30" s="33">
+      <c r="M30" s="34">
         <v>9.9</v>
       </c>
-      <c r="N30" s="33">
+      <c r="N30" s="34">
         <v>9.36</v>
       </c>
-      <c r="O30" s="33">
+      <c r="O30" s="34">
         <v>7.22</v>
       </c>
-      <c r="P30" s="33">
+      <c r="P30" s="34">
         <v>5.41</v>
       </c>
-      <c r="Q30" s="33">
+      <c r="Q30" s="34">
         <v>4.2</v>
       </c>
-      <c r="R30" s="34">
+      <c r="R30" s="35">
         <v>-1.85</v>
       </c>
-      <c r="S30" s="33">
+      <c r="S30" s="34">
         <v>0.8</v>
       </c>
-      <c r="T30" s="34">
+      <c r="T30" s="35">
         <v>-1.87</v>
       </c>
-      <c r="U30" s="33">
+      <c r="U30" s="34">
         <v>1.71</v>
       </c>
-      <c r="V30" s="33">
+      <c r="V30" s="34">
         <v>4.43</v>
       </c>
-      <c r="W30" s="33">
+      <c r="W30" s="34">
         <v>11.82</v>
       </c>
-      <c r="X30" s="33">
+      <c r="X30" s="34">
         <v>22.01</v>
       </c>
-      <c r="Y30" s="33">
+      <c r="Y30" s="34">
         <v>25.86</v>
       </c>
-      <c r="Z30" s="33">
+      <c r="Z30" s="34">
         <v>28.87</v>
       </c>
-      <c r="AA30" s="33">
+      <c r="AA30" s="34">
         <v>28.83</v>
       </c>
-      <c r="AB30" s="33">
+      <c r="AB30" s="34">
         <v>7.61</v>
       </c>
-      <c r="AC30" s="33">
+      <c r="AC30" s="34">
         <v>12.89</v>
       </c>
-      <c r="AD30" s="33">
+      <c r="AD30" s="34">
         <v>134.03</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="29" t="s">
-        <v>507</v>
-      </c>
-      <c r="B31" s="33">
+      <c r="A31" s="30" t="s">
+        <v>508</v>
+      </c>
+      <c r="B31" s="34">
         <v>38.12</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="34">
         <v>36.33</v>
       </c>
-      <c r="D31" s="33">
+      <c r="D31" s="34">
         <v>35.68</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="34">
         <v>7.28</v>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="34">
         <v>7.37</v>
       </c>
-      <c r="G31" s="33">
+      <c r="G31" s="34">
         <v>7.53</v>
       </c>
-      <c r="H31" s="33">
+      <c r="H31" s="34">
         <v>7.23</v>
       </c>
-      <c r="I31" s="33">
+      <c r="I31" s="34">
         <v>7.11</v>
       </c>
-      <c r="J31" s="33">
+      <c r="J31" s="34">
         <v>7.85</v>
       </c>
-      <c r="K31" s="33">
+      <c r="K31" s="34">
         <v>8.33</v>
       </c>
-      <c r="L31" s="33">
+      <c r="L31" s="34">
         <v>7.97</v>
       </c>
-      <c r="M31" s="33">
+      <c r="M31" s="34">
         <v>7.17</v>
       </c>
-      <c r="N31" s="33">
+      <c r="N31" s="34">
         <v>4.95</v>
       </c>
-      <c r="O31" s="33">
+      <c r="O31" s="34">
         <v>3.0</v>
       </c>
-      <c r="P31" s="33">
+      <c r="P31" s="34">
         <v>1.21</v>
       </c>
-      <c r="Q31" s="33">
+      <c r="Q31" s="34">
         <v>0.58</v>
       </c>
-      <c r="R31" s="33">
+      <c r="R31" s="34">
         <v>0.49</v>
       </c>
-      <c r="S31" s="33">
+      <c r="S31" s="34">
         <v>2.27</v>
       </c>
-      <c r="T31" s="33">
+      <c r="T31" s="34">
         <v>4.57</v>
       </c>
-      <c r="U31" s="33">
+      <c r="U31" s="34">
         <v>10.15</v>
       </c>
-      <c r="V31" s="33">
+      <c r="V31" s="34">
         <v>16.07</v>
       </c>
-      <c r="W31" s="33">
+      <c r="W31" s="34">
         <v>22.81</v>
       </c>
-      <c r="X31" s="33">
+      <c r="X31" s="34">
         <v>22.64</v>
       </c>
-      <c r="Y31" s="33">
+      <c r="Y31" s="34">
         <v>20.72</v>
       </c>
-      <c r="Z31" s="33">
+      <c r="Z31" s="34">
         <v>34.02</v>
       </c>
-      <c r="AA31" s="33"/>
-      <c r="AB31" s="33"/>
-      <c r="AC31" s="33"/>
-      <c r="AD31" s="33"/>
+      <c r="AA31" s="34"/>
+      <c r="AB31" s="34"/>
+      <c r="AC31" s="34"/>
+      <c r="AD31" s="34"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="27" t="s">
-        <v>508</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
-      <c r="Y32" s="28"/>
-      <c r="Z32" s="28"/>
-      <c r="AA32" s="28"/>
-      <c r="AB32" s="28"/>
-      <c r="AC32" s="28"/>
-      <c r="AD32" s="28"/>
+      <c r="A32" s="28" t="s">
+        <v>509</v>
+      </c>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="29"/>
+      <c r="T32" s="29"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="29"/>
+      <c r="W32" s="29"/>
+      <c r="X32" s="29"/>
+      <c r="Y32" s="29"/>
+      <c r="Z32" s="29"/>
+      <c r="AA32" s="29"/>
+      <c r="AB32" s="29"/>
+      <c r="AC32" s="29"/>
+      <c r="AD32" s="29"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="29" t="s">
-        <v>509</v>
-      </c>
-      <c r="B33" s="33">
+      <c r="A33" s="30" t="s">
+        <v>510</v>
+      </c>
+      <c r="B33" s="34">
         <v>27.32</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="34">
         <v>21.05</v>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="34">
         <v>18.97</v>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="34">
         <v>2.98</v>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="34">
         <v>6.11</v>
       </c>
-      <c r="G33" s="33">
+      <c r="G33" s="34">
         <v>5.84</v>
       </c>
-      <c r="H33" s="33">
+      <c r="H33" s="34">
         <v>6.15</v>
       </c>
-      <c r="I33" s="33">
+      <c r="I33" s="34">
         <v>5.09</v>
       </c>
-      <c r="J33" s="33">
+      <c r="J33" s="34">
         <v>4.43</v>
       </c>
-      <c r="K33" s="33">
+      <c r="K33" s="34">
         <v>4.14</v>
       </c>
-      <c r="L33" s="33">
+      <c r="L33" s="34">
         <v>3.3</v>
       </c>
-      <c r="M33" s="33">
+      <c r="M33" s="34">
         <v>2.3</v>
       </c>
-      <c r="N33" s="33">
+      <c r="N33" s="34">
         <v>0.0</v>
       </c>
-      <c r="O33" s="33">
+      <c r="O33" s="34">
         <v>4.27</v>
       </c>
-      <c r="P33" s="33">
+      <c r="P33" s="34">
         <v>3.33</v>
       </c>
-      <c r="Q33" s="33">
+      <c r="Q33" s="34">
         <v>3.07</v>
       </c>
-      <c r="R33" s="33">
+      <c r="R33" s="34">
         <v>4.46</v>
       </c>
-      <c r="S33" s="33">
+      <c r="S33" s="34">
         <v>2.16</v>
       </c>
-      <c r="T33" s="33">
+      <c r="T33" s="34">
         <v>1.65</v>
       </c>
-      <c r="U33" s="33"/>
-      <c r="V33" s="33">
+      <c r="U33" s="34"/>
+      <c r="V33" s="34">
         <v>3.32</v>
       </c>
-      <c r="W33" s="33">
+      <c r="W33" s="34">
         <v>1.19</v>
       </c>
-      <c r="X33" s="33">
+      <c r="X33" s="34">
         <v>1.69</v>
       </c>
-      <c r="Y33" s="33">
+      <c r="Y33" s="34">
         <v>2.42</v>
       </c>
-      <c r="Z33" s="33">
+      <c r="Z33" s="34">
         <v>2.34</v>
       </c>
-      <c r="AA33" s="33">
+      <c r="AA33" s="34">
         <v>1.78</v>
       </c>
-      <c r="AB33" s="33">
+      <c r="AB33" s="34">
         <v>1.74</v>
       </c>
-      <c r="AC33" s="33">
+      <c r="AC33" s="34">
         <v>1.12</v>
       </c>
-      <c r="AD33" s="33">
+      <c r="AD33" s="34">
         <v>0.97</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="29" t="s">
-        <v>510</v>
-      </c>
-      <c r="B34" s="33">
+      <c r="A34" s="30" t="s">
+        <v>511</v>
+      </c>
+      <c r="B34" s="34">
         <v>21.17</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="34">
         <v>21.51</v>
       </c>
-      <c r="D34" s="33">
+      <c r="D34" s="34">
         <v>22.75</v>
       </c>
-      <c r="E34" s="33">
+      <c r="E34" s="34">
         <v>5.28</v>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="34">
         <v>5.46</v>
       </c>
-      <c r="G34" s="33">
+      <c r="G34" s="34">
         <v>5.07</v>
       </c>
-      <c r="H34" s="33">
+      <c r="H34" s="34">
         <v>4.61</v>
       </c>
-      <c r="I34" s="33">
+      <c r="I34" s="34">
         <v>3.93</v>
       </c>
-      <c r="J34" s="33">
+      <c r="J34" s="34">
         <v>3.11</v>
       </c>
-      <c r="K34" s="33">
+      <c r="K34" s="34">
         <v>2.92</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="34">
         <v>2.67</v>
       </c>
-      <c r="M34" s="33">
+      <c r="M34" s="34">
         <v>2.61</v>
       </c>
-      <c r="N34" s="33">
+      <c r="N34" s="34">
         <v>3.0</v>
       </c>
-      <c r="O34" s="33">
+      <c r="O34" s="34">
         <v>3.23</v>
       </c>
-      <c r="P34" s="33">
+      <c r="P34" s="34">
         <v>2.7</v>
       </c>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="33"/>
-      <c r="S34" s="33"/>
-      <c r="T34" s="33"/>
-      <c r="U34" s="33"/>
-      <c r="V34" s="33">
+      <c r="Q34" s="34"/>
+      <c r="R34" s="34"/>
+      <c r="S34" s="34"/>
+      <c r="T34" s="34"/>
+      <c r="U34" s="34"/>
+      <c r="V34" s="34">
         <v>2.27</v>
       </c>
-      <c r="W34" s="33">
+      <c r="W34" s="34">
         <v>1.82</v>
       </c>
-      <c r="X34" s="33">
+      <c r="X34" s="34">
         <v>1.98</v>
       </c>
-      <c r="Y34" s="33">
+      <c r="Y34" s="34">
         <v>1.85</v>
       </c>
-      <c r="Z34" s="33">
+      <c r="Z34" s="34">
         <v>1.63</v>
       </c>
-      <c r="AA34" s="33"/>
-      <c r="AB34" s="33"/>
-      <c r="AC34" s="33"/>
-      <c r="AD34" s="33"/>
+      <c r="AA34" s="34"/>
+      <c r="AB34" s="34"/>
+      <c r="AC34" s="34"/>
+      <c r="AD34" s="34"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="29" t="s">
-        <v>511</v>
-      </c>
-      <c r="B35" s="33">
+      <c r="A35" s="30" t="s">
+        <v>512</v>
+      </c>
+      <c r="B35" s="34">
         <v>27.32</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="34">
         <v>21.05</v>
       </c>
-      <c r="D35" s="33">
+      <c r="D35" s="34">
         <v>18.97</v>
       </c>
-      <c r="E35" s="33">
+      <c r="E35" s="34">
         <v>2.98</v>
       </c>
-      <c r="F35" s="33">
+      <c r="F35" s="34">
         <v>6.11</v>
       </c>
-      <c r="G35" s="33">
+      <c r="G35" s="34">
         <v>5.84</v>
       </c>
-      <c r="H35" s="33">
+      <c r="H35" s="34">
         <v>6.15</v>
       </c>
-      <c r="I35" s="33">
+      <c r="I35" s="34">
         <v>5.09</v>
       </c>
-      <c r="J35" s="33">
+      <c r="J35" s="34">
         <v>4.43</v>
       </c>
-      <c r="K35" s="33">
+      <c r="K35" s="34">
         <v>4.14</v>
       </c>
-      <c r="L35" s="33">
+      <c r="L35" s="34">
         <v>3.3</v>
       </c>
-      <c r="M35" s="33">
+      <c r="M35" s="34">
         <v>2.3</v>
       </c>
-      <c r="N35" s="33">
+      <c r="N35" s="34">
         <v>0.0</v>
       </c>
-      <c r="O35" s="33">
+      <c r="O35" s="34">
         <v>5.32</v>
       </c>
-      <c r="P35" s="33">
+      <c r="P35" s="34">
         <v>4.15</v>
       </c>
-      <c r="Q35" s="33">
+      <c r="Q35" s="34">
         <v>3.82</v>
       </c>
-      <c r="R35" s="33">
+      <c r="R35" s="34">
         <v>5.55</v>
       </c>
-      <c r="S35" s="33">
+      <c r="S35" s="34">
         <v>2.69</v>
       </c>
-      <c r="T35" s="33">
+      <c r="T35" s="34">
         <v>2.05</v>
       </c>
-      <c r="U35" s="33">
+      <c r="U35" s="34">
         <v>1.86</v>
       </c>
-      <c r="V35" s="33">
+      <c r="V35" s="34">
         <v>4.88</v>
       </c>
-      <c r="W35" s="33">
+      <c r="W35" s="34">
         <v>1.19</v>
       </c>
-      <c r="X35" s="33">
+      <c r="X35" s="34">
         <v>1.69</v>
       </c>
-      <c r="Y35" s="33">
+      <c r="Y35" s="34">
         <v>2.42</v>
       </c>
-      <c r="Z35" s="33">
+      <c r="Z35" s="34">
         <v>2.34</v>
       </c>
-      <c r="AA35" s="33">
+      <c r="AA35" s="34">
         <v>1.78</v>
       </c>
-      <c r="AB35" s="33">
+      <c r="AB35" s="34">
         <v>1.74</v>
       </c>
-      <c r="AC35" s="33">
+      <c r="AC35" s="34">
         <v>1.12</v>
       </c>
-      <c r="AD35" s="33">
+      <c r="AD35" s="34">
         <v>0.97</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="29" t="s">
-        <v>512</v>
-      </c>
-      <c r="B36" s="33">
+      <c r="A36" s="30" t="s">
+        <v>513</v>
+      </c>
+      <c r="B36" s="34">
         <v>21.17</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="34">
         <v>21.51</v>
       </c>
-      <c r="D36" s="33">
+      <c r="D36" s="34">
         <v>22.75</v>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="34">
         <v>5.28</v>
       </c>
-      <c r="F36" s="33">
+      <c r="F36" s="34">
         <v>5.46</v>
       </c>
-      <c r="G36" s="33">
+      <c r="G36" s="34">
         <v>5.07</v>
       </c>
-      <c r="H36" s="33">
+      <c r="H36" s="34">
         <v>4.61</v>
       </c>
-      <c r="I36" s="33">
+      <c r="I36" s="34">
         <v>3.93</v>
       </c>
-      <c r="J36" s="33">
+      <c r="J36" s="34">
         <v>3.11</v>
       </c>
-      <c r="K36" s="33">
+      <c r="K36" s="34">
         <v>3.08</v>
       </c>
-      <c r="L36" s="33">
+      <c r="L36" s="34">
         <v>3.0</v>
       </c>
-      <c r="M36" s="33">
+      <c r="M36" s="34">
         <v>3.11</v>
       </c>
-      <c r="N36" s="33">
+      <c r="N36" s="34">
         <v>3.73</v>
       </c>
-      <c r="O36" s="33">
+      <c r="O36" s="34">
         <v>4.02</v>
       </c>
-      <c r="P36" s="33">
+      <c r="P36" s="34">
         <v>3.35</v>
       </c>
-      <c r="Q36" s="33">
+      <c r="Q36" s="34">
         <v>2.96</v>
       </c>
-      <c r="R36" s="33">
+      <c r="R36" s="34">
         <v>3.1</v>
       </c>
-      <c r="S36" s="33">
+      <c r="S36" s="34">
         <v>2.53</v>
       </c>
-      <c r="T36" s="33">
+      <c r="T36" s="34">
         <v>2.39</v>
       </c>
-      <c r="U36" s="33">
+      <c r="U36" s="34">
         <v>2.54</v>
       </c>
-      <c r="V36" s="33">
+      <c r="V36" s="34">
         <v>2.73</v>
       </c>
-      <c r="W36" s="33">
+      <c r="W36" s="34">
         <v>1.82</v>
       </c>
-      <c r="X36" s="33">
+      <c r="X36" s="34">
         <v>1.98</v>
       </c>
-      <c r="Y36" s="33">
+      <c r="Y36" s="34">
         <v>1.85</v>
       </c>
-      <c r="Z36" s="33">
+      <c r="Z36" s="34">
         <v>1.63</v>
       </c>
-      <c r="AA36" s="33"/>
-      <c r="AB36" s="33"/>
-      <c r="AC36" s="33"/>
-      <c r="AD36" s="33"/>
+      <c r="AA36" s="34"/>
+      <c r="AB36" s="34"/>
+      <c r="AC36" s="34"/>
+      <c r="AD36" s="34"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="27" t="s">
-        <v>513</v>
-      </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
-      <c r="U37" s="28"/>
-      <c r="V37" s="28"/>
-      <c r="W37" s="28"/>
-      <c r="X37" s="28"/>
-      <c r="Y37" s="28"/>
-      <c r="Z37" s="28"/>
-      <c r="AA37" s="28"/>
-      <c r="AB37" s="28"/>
-      <c r="AC37" s="28"/>
-      <c r="AD37" s="28"/>
+      <c r="A37" s="28" t="s">
+        <v>514</v>
+      </c>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="29"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="29"/>
+      <c r="W37" s="29"/>
+      <c r="X37" s="29"/>
+      <c r="Y37" s="29"/>
+      <c r="Z37" s="29"/>
+      <c r="AA37" s="29"/>
+      <c r="AB37" s="29"/>
+      <c r="AC37" s="29"/>
+      <c r="AD37" s="29"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="29" t="s">
-        <v>514</v>
-      </c>
-      <c r="B38" s="32">
+      <c r="A38" s="30" t="s">
+        <v>515</v>
+      </c>
+      <c r="B38" s="33">
         <v>0.33</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="33">
         <v>0.37</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="33">
         <v>0.42</v>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="33">
         <v>2.43</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="33">
         <v>2.98</v>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="33">
         <v>2.96</v>
       </c>
-      <c r="H38" s="32">
+      <c r="H38" s="33">
         <v>2.71</v>
       </c>
-      <c r="I38" s="32">
+      <c r="I38" s="33">
         <v>3.19</v>
       </c>
-      <c r="J38" s="32">
+      <c r="J38" s="33">
         <v>3.31</v>
       </c>
-      <c r="K38" s="32">
+      <c r="K38" s="33">
         <v>3.29</v>
       </c>
-      <c r="L38" s="32">
+      <c r="L38" s="33">
         <v>2.84</v>
       </c>
-      <c r="M38" s="32">
+      <c r="M38" s="33">
         <v>2.79</v>
       </c>
-      <c r="N38" s="32">
+      <c r="N38" s="33">
         <v>1.83</v>
       </c>
-      <c r="O38" s="32">
+      <c r="O38" s="33">
         <v>1.84</v>
       </c>
-      <c r="P38" s="32">
+      <c r="P38" s="33">
         <v>2.31</v>
       </c>
-      <c r="Q38" s="32">
+      <c r="Q38" s="33">
         <v>2.57</v>
       </c>
-      <c r="R38" s="32">
+      <c r="R38" s="33">
         <v>1.88</v>
       </c>
-      <c r="S38" s="32">
+      <c r="S38" s="33">
         <v>3.92</v>
       </c>
-      <c r="T38" s="32">
+      <c r="T38" s="33">
         <v>4.32</v>
       </c>
-      <c r="U38" s="32">
+      <c r="U38" s="33">
         <v>3.37</v>
       </c>
-      <c r="V38" s="32">
+      <c r="V38" s="33">
         <v>3.38</v>
       </c>
-      <c r="W38" s="32">
+      <c r="W38" s="33">
         <v>4.09</v>
       </c>
-      <c r="X38" s="32">
+      <c r="X38" s="33">
         <v>2.57</v>
       </c>
-      <c r="Y38" s="32">
+      <c r="Y38" s="33">
         <v>3.22</v>
       </c>
-      <c r="Z38" s="32">
+      <c r="Z38" s="33">
         <v>1.97</v>
       </c>
-      <c r="AA38" s="32">
+      <c r="AA38" s="33">
         <v>2.69</v>
       </c>
-      <c r="AB38" s="32">
+      <c r="AB38" s="33">
         <v>0.97</v>
       </c>
-      <c r="AC38" s="32">
+      <c r="AC38" s="33">
         <v>1.09</v>
       </c>
-      <c r="AD38" s="32">
+      <c r="AD38" s="33">
         <v>0.19</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="29" t="s">
-        <v>515</v>
-      </c>
-      <c r="B39" s="32">
+      <c r="A39" s="30" t="s">
+        <v>516</v>
+      </c>
+      <c r="B39" s="33">
         <v>0.46</v>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="33">
         <v>0.53</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="33">
         <v>0.59</v>
       </c>
-      <c r="E39" s="32">
+      <c r="E39" s="33">
         <v>2.85</v>
       </c>
-      <c r="F39" s="32">
+      <c r="F39" s="33">
         <v>3.03</v>
       </c>
-      <c r="G39" s="32">
+      <c r="G39" s="33">
         <v>3.09</v>
       </c>
-      <c r="H39" s="32">
+      <c r="H39" s="33">
         <v>3.07</v>
       </c>
-      <c r="I39" s="32">
+      <c r="I39" s="33">
         <v>3.09</v>
       </c>
-      <c r="J39" s="32">
+      <c r="J39" s="33">
         <v>2.8</v>
       </c>
-      <c r="K39" s="32">
+      <c r="K39" s="33">
         <v>2.5</v>
       </c>
-      <c r="L39" s="32">
+      <c r="L39" s="33">
         <v>2.31</v>
       </c>
-      <c r="M39" s="32">
+      <c r="M39" s="33">
         <v>2.26</v>
       </c>
-      <c r="N39" s="32">
+      <c r="N39" s="33">
         <v>2.08</v>
       </c>
-      <c r="O39" s="32">
+      <c r="O39" s="33">
         <v>2.49</v>
       </c>
-      <c r="P39" s="32">
+      <c r="P39" s="33">
         <v>2.94</v>
       </c>
-      <c r="Q39" s="32">
+      <c r="Q39" s="33">
         <v>3.16</v>
       </c>
-      <c r="R39" s="32">
+      <c r="R39" s="33">
         <v>3.34</v>
       </c>
-      <c r="S39" s="32">
+      <c r="S39" s="33">
         <v>3.83</v>
       </c>
-      <c r="T39" s="32">
+      <c r="T39" s="33">
         <v>3.63</v>
       </c>
-      <c r="U39" s="32">
+      <c r="U39" s="33">
         <v>3.35</v>
       </c>
-      <c r="V39" s="32">
+      <c r="V39" s="33">
         <v>3.0</v>
       </c>
-      <c r="W39" s="32">
+      <c r="W39" s="33">
         <v>2.82</v>
       </c>
-      <c r="X39" s="32">
+      <c r="X39" s="33">
         <v>1.89</v>
       </c>
-      <c r="Y39" s="32">
+      <c r="Y39" s="33">
         <v>1.58</v>
       </c>
-      <c r="Z39" s="32">
+      <c r="Z39" s="33">
         <v>0.79</v>
       </c>
-      <c r="AA39" s="31"/>
-      <c r="AB39" s="31"/>
-      <c r="AC39" s="31"/>
-      <c r="AD39" s="31"/>
+      <c r="AA39" s="32"/>
+      <c r="AB39" s="32"/>
+      <c r="AC39" s="32"/>
+      <c r="AD39" s="32"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="27" t="s">
-        <v>516</v>
-      </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
-      <c r="T40" s="28"/>
-      <c r="U40" s="28"/>
-      <c r="V40" s="28"/>
-      <c r="W40" s="28"/>
-      <c r="X40" s="28"/>
-      <c r="Y40" s="28"/>
-      <c r="Z40" s="28"/>
-      <c r="AA40" s="28"/>
-      <c r="AB40" s="28"/>
-      <c r="AC40" s="28"/>
-      <c r="AD40" s="28"/>
+      <c r="A40" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="29"/>
+      <c r="S40" s="29"/>
+      <c r="T40" s="29"/>
+      <c r="U40" s="29"/>
+      <c r="V40" s="29"/>
+      <c r="W40" s="29"/>
+      <c r="X40" s="29"/>
+      <c r="Y40" s="29"/>
+      <c r="Z40" s="29"/>
+      <c r="AA40" s="29"/>
+      <c r="AB40" s="29"/>
+      <c r="AC40" s="29"/>
+      <c r="AD40" s="29"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="29" t="s">
-        <v>517</v>
-      </c>
-      <c r="B41" s="32">
+      <c r="A41" s="30" t="s">
+        <v>518</v>
+      </c>
+      <c r="B41" s="33">
         <v>6.85</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="33">
         <v>6.45</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="33">
         <v>28.9</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="33">
         <v>88.32</v>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="33">
         <v>59.18</v>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="33">
         <v>40.51</v>
       </c>
-      <c r="H41" s="32">
+      <c r="H41" s="33">
         <v>30.89</v>
       </c>
-      <c r="I41" s="32">
+      <c r="I41" s="33">
         <v>33.18</v>
       </c>
-      <c r="J41" s="32">
+      <c r="J41" s="33">
         <v>9.26</v>
       </c>
-      <c r="K41" s="32">
+      <c r="K41" s="33">
         <v>9.1</v>
       </c>
-      <c r="L41" s="32">
+      <c r="L41" s="33">
         <v>7.27</v>
       </c>
-      <c r="M41" s="32">
+      <c r="M41" s="33">
         <v>6.94</v>
       </c>
-      <c r="N41" s="32">
+      <c r="N41" s="33">
         <v>4.51</v>
       </c>
-      <c r="O41" s="32">
+      <c r="O41" s="33">
         <v>5.47</v>
       </c>
-      <c r="P41" s="32">
+      <c r="P41" s="33">
         <v>7.69</v>
       </c>
-      <c r="Q41" s="32">
+      <c r="Q41" s="33">
         <v>10.15</v>
       </c>
-      <c r="R41" s="32">
+      <c r="R41" s="33">
         <v>9.41</v>
       </c>
-      <c r="S41" s="32">
+      <c r="S41" s="33">
         <v>16.22</v>
       </c>
-      <c r="T41" s="32">
+      <c r="T41" s="33">
         <v>12.6</v>
       </c>
-      <c r="U41" s="31"/>
-      <c r="V41" s="31"/>
-      <c r="W41" s="32">
+      <c r="U41" s="32"/>
+      <c r="V41" s="32"/>
+      <c r="W41" s="33">
         <v>40.22</v>
       </c>
-      <c r="X41" s="30">
+      <c r="X41" s="31">
         <v>101.06</v>
       </c>
-      <c r="Y41" s="31"/>
-      <c r="Z41" s="32">
+      <c r="Y41" s="32"/>
+      <c r="Z41" s="33">
         <v>1.97</v>
       </c>
-      <c r="AA41" s="32">
+      <c r="AA41" s="33">
         <v>3.0</v>
       </c>
-      <c r="AB41" s="32">
+      <c r="AB41" s="33">
         <v>1.04</v>
       </c>
-      <c r="AC41" s="32">
+      <c r="AC41" s="33">
         <v>1.16</v>
       </c>
-      <c r="AD41" s="32">
+      <c r="AD41" s="33">
         <v>0.21</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="29" t="s">
-        <v>518</v>
-      </c>
-      <c r="B42" s="32">
+      <c r="A42" s="30" t="s">
+        <v>519</v>
+      </c>
+      <c r="B42" s="33">
         <v>11.79</v>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="33">
         <v>12.03</v>
       </c>
-      <c r="D42" s="32">
+      <c r="D42" s="33">
         <v>11.67</v>
       </c>
-      <c r="E42" s="32">
+      <c r="E42" s="33">
         <v>42.36</v>
       </c>
-      <c r="F42" s="32">
+      <c r="F42" s="33">
         <v>22.16</v>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="33">
         <v>15.7</v>
       </c>
-      <c r="H42" s="32">
+      <c r="H42" s="33">
         <v>11.91</v>
       </c>
-      <c r="I42" s="32">
+      <c r="I42" s="33">
         <v>9.65</v>
       </c>
-      <c r="J42" s="32">
+      <c r="J42" s="33">
         <v>7.3</v>
       </c>
-      <c r="K42" s="32">
+      <c r="K42" s="33">
         <v>6.59</v>
       </c>
-      <c r="L42" s="32">
+      <c r="L42" s="33">
         <v>6.29</v>
       </c>
-      <c r="M42" s="32">
+      <c r="M42" s="33">
         <v>6.65</v>
       </c>
-      <c r="N42" s="32">
+      <c r="N42" s="33">
         <v>6.91</v>
       </c>
-      <c r="O42" s="32">
+      <c r="O42" s="33">
         <v>11.99</v>
       </c>
-      <c r="P42" s="32">
+      <c r="P42" s="33">
         <v>14.46</v>
       </c>
-      <c r="Q42" s="32">
+      <c r="Q42" s="33">
         <v>51.5</v>
       </c>
-      <c r="R42" s="30">
+      <c r="R42" s="31">
         <v>272.4</v>
       </c>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
-      <c r="U42" s="31"/>
-      <c r="V42" s="32">
+      <c r="S42" s="32"/>
+      <c r="T42" s="32"/>
+      <c r="U42" s="32"/>
+      <c r="V42" s="33">
         <v>24.34</v>
       </c>
-      <c r="W42" s="32">
+      <c r="W42" s="33">
         <v>5.68</v>
       </c>
-      <c r="X42" s="32">
+      <c r="X42" s="33">
         <v>2.57</v>
       </c>
-      <c r="Y42" s="32">
+      <c r="Y42" s="33">
         <v>1.84</v>
       </c>
-      <c r="Z42" s="32">
+      <c r="Z42" s="33">
         <v>0.85</v>
       </c>
-      <c r="AA42" s="31"/>
-      <c r="AB42" s="31"/>
-      <c r="AC42" s="31"/>
-      <c r="AD42" s="31"/>
+      <c r="AA42" s="32"/>
+      <c r="AB42" s="32"/>
+      <c r="AC42" s="32"/>
+      <c r="AD42" s="32"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="27" t="s">
-        <v>519</v>
-      </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="28"/>
-      <c r="S43" s="28"/>
-      <c r="T43" s="28"/>
-      <c r="U43" s="28"/>
-      <c r="V43" s="28"/>
-      <c r="W43" s="28"/>
-      <c r="X43" s="28"/>
-      <c r="Y43" s="28"/>
-      <c r="Z43" s="28"/>
-      <c r="AA43" s="28"/>
-      <c r="AB43" s="28"/>
-      <c r="AC43" s="28"/>
-      <c r="AD43" s="28"/>
+      <c r="A43" s="28" t="s">
+        <v>520</v>
+      </c>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="29"/>
+      <c r="S43" s="29"/>
+      <c r="T43" s="29"/>
+      <c r="U43" s="29"/>
+      <c r="V43" s="29"/>
+      <c r="W43" s="29"/>
+      <c r="X43" s="29"/>
+      <c r="Y43" s="29"/>
+      <c r="Z43" s="29"/>
+      <c r="AA43" s="29"/>
+      <c r="AB43" s="29"/>
+      <c r="AC43" s="29"/>
+      <c r="AD43" s="29"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="29" t="s">
-        <v>520</v>
-      </c>
-      <c r="B44" s="32">
+      <c r="A44" s="30" t="s">
+        <v>521</v>
+      </c>
+      <c r="B44" s="33">
         <v>0.09</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="33">
         <v>0.11</v>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="33">
         <v>0.11</v>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="33">
         <v>0.63</v>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="33">
         <v>0.76</v>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="33">
         <v>0.77</v>
       </c>
-      <c r="H44" s="32">
+      <c r="H44" s="33">
         <v>0.72</v>
       </c>
-      <c r="I44" s="32">
+      <c r="I44" s="33">
         <v>0.98</v>
       </c>
-      <c r="J44" s="32">
+      <c r="J44" s="33">
         <v>1.11</v>
       </c>
-      <c r="K44" s="32">
+      <c r="K44" s="33">
         <v>1.08</v>
       </c>
-      <c r="L44" s="32">
+      <c r="L44" s="33">
         <v>0.92</v>
       </c>
-      <c r="M44" s="32">
+      <c r="M44" s="33">
         <v>0.88</v>
       </c>
-      <c r="N44" s="32">
+      <c r="N44" s="33">
         <v>0.63</v>
       </c>
-      <c r="O44" s="32">
+      <c r="O44" s="33">
         <v>0.62</v>
       </c>
-      <c r="P44" s="32">
+      <c r="P44" s="33">
         <v>0.86</v>
       </c>
-      <c r="Q44" s="32">
+      <c r="Q44" s="33">
         <v>0.96</v>
       </c>
-      <c r="R44" s="32">
+      <c r="R44" s="33">
         <v>0.63</v>
       </c>
-      <c r="S44" s="32">
+      <c r="S44" s="33">
         <v>1.43</v>
       </c>
-      <c r="T44" s="32">
+      <c r="T44" s="33">
         <v>1.73</v>
       </c>
-      <c r="U44" s="32">
+      <c r="U44" s="33">
         <v>1.37</v>
       </c>
-      <c r="V44" s="32">
+      <c r="V44" s="33">
         <v>1.22</v>
       </c>
-      <c r="W44" s="32">
+      <c r="W44" s="33">
         <v>0.5</v>
       </c>
-      <c r="X44" s="32">
+      <c r="X44" s="33">
         <v>0.32</v>
       </c>
-      <c r="Y44" s="32">
+      <c r="Y44" s="33">
         <v>0.41</v>
       </c>
-      <c r="Z44" s="32">
+      <c r="Z44" s="33">
         <v>0.27</v>
       </c>
-      <c r="AA44" s="32">
+      <c r="AA44" s="33">
         <v>0.42</v>
       </c>
-      <c r="AB44" s="32">
+      <c r="AB44" s="33">
         <v>0.38</v>
       </c>
-      <c r="AC44" s="32">
+      <c r="AC44" s="33">
         <v>0.4</v>
       </c>
-      <c r="AD44" s="32">
+      <c r="AD44" s="33">
         <v>0.06</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="29" t="s">
-        <v>521</v>
-      </c>
-      <c r="B45" s="32">
+      <c r="A45" s="30" t="s">
+        <v>522</v>
+      </c>
+      <c r="B45" s="33">
         <v>0.12</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="33">
         <v>0.14</v>
       </c>
-      <c r="D45" s="32">
+      <c r="D45" s="33">
         <v>0.15</v>
       </c>
-      <c r="E45" s="32">
+      <c r="E45" s="33">
         <v>0.77</v>
       </c>
-      <c r="F45" s="32">
+      <c r="F45" s="33">
         <v>0.86</v>
       </c>
-      <c r="G45" s="32">
+      <c r="G45" s="33">
         <v>0.92</v>
       </c>
-      <c r="H45" s="32">
+      <c r="H45" s="33">
         <v>0.95</v>
       </c>
-      <c r="I45" s="32">
+      <c r="I45" s="33">
         <v>0.99</v>
       </c>
-      <c r="J45" s="32">
+      <c r="J45" s="33">
         <v>0.92</v>
       </c>
-      <c r="K45" s="32">
+      <c r="K45" s="33">
         <v>0.82</v>
       </c>
-      <c r="L45" s="32">
+      <c r="L45" s="33">
         <v>0.78</v>
       </c>
-      <c r="M45" s="32">
+      <c r="M45" s="33">
         <v>0.78</v>
       </c>
-      <c r="N45" s="32">
+      <c r="N45" s="33">
         <v>0.73</v>
       </c>
-      <c r="O45" s="32">
+      <c r="O45" s="33">
         <v>0.89</v>
       </c>
-      <c r="P45" s="32">
+      <c r="P45" s="33">
         <v>1.08</v>
       </c>
-      <c r="Q45" s="32">
+      <c r="Q45" s="33">
         <v>1.18</v>
       </c>
-      <c r="R45" s="32">
+      <c r="R45" s="33">
         <v>1.24</v>
       </c>
-      <c r="S45" s="32">
+      <c r="S45" s="33">
         <v>1.16</v>
       </c>
-      <c r="T45" s="32">
+      <c r="T45" s="33">
         <v>0.89</v>
       </c>
-      <c r="U45" s="32">
+      <c r="U45" s="33">
         <v>0.66</v>
       </c>
-      <c r="V45" s="32">
+      <c r="V45" s="33">
         <v>0.46</v>
       </c>
-      <c r="W45" s="32">
+      <c r="W45" s="33">
         <v>0.38</v>
       </c>
-      <c r="X45" s="32">
+      <c r="X45" s="33">
         <v>0.36</v>
       </c>
-      <c r="Y45" s="32">
+      <c r="Y45" s="33">
         <v>0.37</v>
       </c>
-      <c r="Z45" s="32">
+      <c r="Z45" s="33">
         <v>0.23</v>
       </c>
-      <c r="AA45" s="31"/>
-      <c r="AB45" s="31"/>
-      <c r="AC45" s="31"/>
-      <c r="AD45" s="31"/>
+      <c r="AA45" s="32"/>
+      <c r="AB45" s="32"/>
+      <c r="AC45" s="32"/>
+      <c r="AD45" s="32"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="27" t="s">
-        <v>522</v>
-      </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="28"/>
-      <c r="P46" s="28"/>
-      <c r="Q46" s="28"/>
-      <c r="R46" s="28"/>
-      <c r="S46" s="28"/>
-      <c r="T46" s="28"/>
-      <c r="U46" s="28"/>
-      <c r="V46" s="28"/>
-      <c r="W46" s="28"/>
-      <c r="X46" s="28"/>
-      <c r="Y46" s="28"/>
-      <c r="Z46" s="28"/>
-      <c r="AA46" s="28"/>
-      <c r="AB46" s="28"/>
-      <c r="AC46" s="28"/>
-      <c r="AD46" s="28"/>
+      <c r="A46" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="29"/>
+      <c r="W46" s="29"/>
+      <c r="X46" s="29"/>
+      <c r="Y46" s="29"/>
+      <c r="Z46" s="29"/>
+      <c r="AA46" s="29"/>
+      <c r="AB46" s="29"/>
+      <c r="AC46" s="29"/>
+      <c r="AD46" s="29"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="29" t="s">
-        <v>523</v>
-      </c>
-      <c r="B47" s="32">
+      <c r="A47" s="30" t="s">
+        <v>524</v>
+      </c>
+      <c r="B47" s="33">
         <v>1.69</v>
       </c>
-      <c r="C47" s="32">
+      <c r="C47" s="33">
         <v>1.76</v>
       </c>
-      <c r="D47" s="32">
+      <c r="D47" s="33">
         <v>2.43</v>
       </c>
-      <c r="E47" s="32">
+      <c r="E47" s="33">
         <v>21.98</v>
       </c>
-      <c r="F47" s="32">
+      <c r="F47" s="33">
         <v>15.1</v>
       </c>
-      <c r="G47" s="32">
+      <c r="G47" s="33">
         <v>10.62</v>
       </c>
-      <c r="H47" s="32">
+      <c r="H47" s="33">
         <v>9.4</v>
       </c>
-      <c r="I47" s="32">
+      <c r="I47" s="33">
         <v>19.1</v>
       </c>
-      <c r="J47" s="32">
+      <c r="J47" s="33">
         <v>17.34</v>
       </c>
-      <c r="K47" s="32">
+      <c r="K47" s="33">
         <v>13.32</v>
       </c>
-      <c r="L47" s="32">
+      <c r="L47" s="33">
         <v>12.89</v>
       </c>
-      <c r="M47" s="32">
+      <c r="M47" s="33">
         <v>10.1</v>
       </c>
-      <c r="N47" s="32">
+      <c r="N47" s="33">
         <v>10.69</v>
       </c>
-      <c r="O47" s="32">
+      <c r="O47" s="33">
         <v>13.85</v>
       </c>
-      <c r="P47" s="32">
+      <c r="P47" s="33">
         <v>18.48</v>
       </c>
-      <c r="Q47" s="32">
+      <c r="Q47" s="33">
         <v>23.81</v>
       </c>
-      <c r="R47" s="31"/>
-      <c r="S47" s="30">
+      <c r="R47" s="32"/>
+      <c r="S47" s="31">
         <v>125.49</v>
       </c>
-      <c r="T47" s="31"/>
-      <c r="U47" s="32">
+      <c r="T47" s="32"/>
+      <c r="U47" s="33">
         <v>58.61</v>
       </c>
-      <c r="V47" s="32">
+      <c r="V47" s="33">
         <v>22.58</v>
       </c>
-      <c r="W47" s="32">
+      <c r="W47" s="33">
         <v>8.46</v>
       </c>
-      <c r="X47" s="32">
+      <c r="X47" s="33">
         <v>4.54</v>
       </c>
-      <c r="Y47" s="32">
+      <c r="Y47" s="33">
         <v>3.87</v>
       </c>
-      <c r="Z47" s="32">
+      <c r="Z47" s="33">
         <v>3.46</v>
       </c>
-      <c r="AA47" s="32">
+      <c r="AA47" s="33">
         <v>3.47</v>
       </c>
-      <c r="AB47" s="32">
+      <c r="AB47" s="33">
         <v>13.15</v>
       </c>
-      <c r="AC47" s="32">
+      <c r="AC47" s="33">
         <v>7.76</v>
       </c>
-      <c r="AD47" s="32">
+      <c r="AD47" s="33">
         <v>0.75</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="29" t="s">
-        <v>524</v>
-      </c>
-      <c r="B48" s="32">
+      <c r="A48" s="30" t="s">
+        <v>525</v>
+      </c>
+      <c r="B48" s="33">
         <v>2.62</v>
       </c>
-      <c r="C48" s="32">
+      <c r="C48" s="33">
         <v>2.75</v>
       </c>
-      <c r="D48" s="32">
+      <c r="D48" s="33">
         <v>2.8</v>
       </c>
-      <c r="E48" s="32">
+      <c r="E48" s="33">
         <v>13.73</v>
       </c>
-      <c r="F48" s="32">
+      <c r="F48" s="33">
         <v>13.56</v>
       </c>
-      <c r="G48" s="32">
+      <c r="G48" s="33">
         <v>13.27</v>
       </c>
-      <c r="H48" s="32">
+      <c r="H48" s="33">
         <v>13.83</v>
       </c>
-      <c r="I48" s="32">
+      <c r="I48" s="33">
         <v>14.07</v>
       </c>
-      <c r="J48" s="32">
+      <c r="J48" s="33">
         <v>12.73</v>
       </c>
-      <c r="K48" s="32">
+      <c r="K48" s="33">
         <v>12.0</v>
       </c>
-      <c r="L48" s="32">
+      <c r="L48" s="33">
         <v>12.55</v>
       </c>
-      <c r="M48" s="32">
+      <c r="M48" s="33">
         <v>13.95</v>
       </c>
-      <c r="N48" s="32">
+      <c r="N48" s="33">
         <v>20.21</v>
       </c>
-      <c r="O48" s="32">
+      <c r="O48" s="33">
         <v>33.36</v>
       </c>
-      <c r="P48" s="32">
+      <c r="P48" s="33">
         <v>82.72</v>
       </c>
-      <c r="Q48" s="30">
+      <c r="Q48" s="31">
         <v>173.18</v>
       </c>
-      <c r="R48" s="30">
+      <c r="R48" s="31">
         <v>204.41</v>
       </c>
-      <c r="S48" s="32">
+      <c r="S48" s="33">
         <v>44.1</v>
       </c>
-      <c r="T48" s="32">
+      <c r="T48" s="33">
         <v>21.87</v>
       </c>
-      <c r="U48" s="32">
+      <c r="U48" s="33">
         <v>9.85</v>
       </c>
-      <c r="V48" s="32">
+      <c r="V48" s="33">
         <v>6.22</v>
       </c>
-      <c r="W48" s="32">
+      <c r="W48" s="33">
         <v>4.38</v>
       </c>
-      <c r="X48" s="32">
+      <c r="X48" s="33">
         <v>4.42</v>
       </c>
-      <c r="Y48" s="32">
+      <c r="Y48" s="33">
         <v>4.83</v>
       </c>
-      <c r="Z48" s="32">
+      <c r="Z48" s="33">
         <v>2.94</v>
       </c>
-      <c r="AA48" s="31"/>
-      <c r="AB48" s="31"/>
-      <c r="AC48" s="31"/>
-      <c r="AD48" s="31"/>
+      <c r="AA48" s="32"/>
+      <c r="AB48" s="32"/>
+      <c r="AC48" s="32"/>
+      <c r="AD48" s="32"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="27" t="s">
-        <v>525</v>
-      </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
-      <c r="M49" s="28"/>
-      <c r="N49" s="28"/>
-      <c r="O49" s="28"/>
-      <c r="P49" s="28"/>
-      <c r="Q49" s="28"/>
-      <c r="R49" s="28"/>
-      <c r="S49" s="28"/>
-      <c r="T49" s="28"/>
-      <c r="U49" s="28"/>
-      <c r="V49" s="28"/>
-      <c r="W49" s="28"/>
-      <c r="X49" s="28"/>
-      <c r="Y49" s="28"/>
-      <c r="Z49" s="28"/>
-      <c r="AA49" s="28"/>
-      <c r="AB49" s="28"/>
-      <c r="AC49" s="28"/>
-      <c r="AD49" s="28"/>
+      <c r="A49" s="28" t="s">
+        <v>526</v>
+      </c>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29"/>
+      <c r="O49" s="29"/>
+      <c r="P49" s="29"/>
+      <c r="Q49" s="29"/>
+      <c r="R49" s="29"/>
+      <c r="S49" s="29"/>
+      <c r="T49" s="29"/>
+      <c r="U49" s="29"/>
+      <c r="V49" s="29"/>
+      <c r="W49" s="29"/>
+      <c r="X49" s="29"/>
+      <c r="Y49" s="29"/>
+      <c r="Z49" s="29"/>
+      <c r="AA49" s="29"/>
+      <c r="AB49" s="29"/>
+      <c r="AC49" s="29"/>
+      <c r="AD49" s="29"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="29" t="s">
-        <v>526</v>
-      </c>
-      <c r="B50" s="32">
+      <c r="A50" s="30" t="s">
+        <v>527</v>
+      </c>
+      <c r="B50" s="33">
         <v>1.26</v>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="33">
         <v>1.0</v>
       </c>
-      <c r="D50" s="32">
+      <c r="D50" s="33">
         <v>1.06</v>
       </c>
-      <c r="E50" s="32">
+      <c r="E50" s="33">
         <v>5.86</v>
       </c>
-      <c r="F50" s="32">
+      <c r="F50" s="33">
         <v>7.54</v>
       </c>
-      <c r="G50" s="32">
+      <c r="G50" s="33">
         <v>8.3</v>
       </c>
-      <c r="H50" s="32">
+      <c r="H50" s="33">
         <v>7.5</v>
       </c>
-      <c r="I50" s="32">
+      <c r="I50" s="33">
         <v>9.28</v>
       </c>
-      <c r="J50" s="32">
+      <c r="J50" s="33">
         <v>8.97</v>
       </c>
-      <c r="K50" s="32">
+      <c r="K50" s="33">
         <v>8.91</v>
       </c>
-      <c r="L50" s="32">
+      <c r="L50" s="33">
         <v>10.04</v>
       </c>
-      <c r="M50" s="32">
+      <c r="M50" s="33">
         <v>9.19</v>
       </c>
-      <c r="N50" s="32">
+      <c r="N50" s="33">
         <v>5.47</v>
       </c>
-      <c r="O50" s="32">
+      <c r="O50" s="33">
         <v>5.11</v>
       </c>
-      <c r="P50" s="32">
+      <c r="P50" s="33">
         <v>7.33</v>
       </c>
-      <c r="Q50" s="32">
+      <c r="Q50" s="33">
         <v>6.51</v>
       </c>
-      <c r="R50" s="32">
+      <c r="R50" s="33">
         <v>4.75</v>
       </c>
-      <c r="S50" s="32">
+      <c r="S50" s="33">
         <v>14.85</v>
       </c>
-      <c r="T50" s="32">
+      <c r="T50" s="33">
         <v>11.87</v>
       </c>
-      <c r="U50" s="32">
+      <c r="U50" s="33">
         <v>9.91</v>
       </c>
-      <c r="V50" s="32">
+      <c r="V50" s="33">
         <v>7.25</v>
       </c>
-      <c r="W50" s="32">
+      <c r="W50" s="33">
         <v>3.22</v>
       </c>
-      <c r="X50" s="32">
+      <c r="X50" s="33">
         <v>2.27</v>
       </c>
-      <c r="Y50" s="32">
+      <c r="Y50" s="33">
         <v>3.34</v>
       </c>
-      <c r="Z50" s="32">
+      <c r="Z50" s="33">
         <v>1.88</v>
       </c>
-      <c r="AA50" s="32">
+      <c r="AA50" s="33">
         <v>3.63</v>
       </c>
-      <c r="AB50" s="32">
+      <c r="AB50" s="33">
         <v>2.45</v>
       </c>
-      <c r="AC50" s="32">
+      <c r="AC50" s="33">
         <v>2.75</v>
       </c>
-      <c r="AD50" s="32">
+      <c r="AD50" s="33">
         <v>0.45</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="29" t="s">
-        <v>527</v>
-      </c>
-      <c r="B51" s="32">
+      <c r="A51" s="30" t="s">
+        <v>528</v>
+      </c>
+      <c r="B51" s="33">
         <v>1.27</v>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="33">
         <v>1.38</v>
       </c>
-      <c r="D51" s="32">
+      <c r="D51" s="33">
         <v>1.52</v>
       </c>
-      <c r="E51" s="32">
+      <c r="E51" s="33">
         <v>7.63</v>
       </c>
-      <c r="F51" s="32">
+      <c r="F51" s="33">
         <v>8.32</v>
       </c>
-      <c r="G51" s="32">
+      <c r="G51" s="33">
         <v>8.6</v>
       </c>
-      <c r="H51" s="32">
+      <c r="H51" s="33">
         <v>8.88</v>
       </c>
-      <c r="I51" s="32">
+      <c r="I51" s="33">
         <v>9.24</v>
       </c>
-      <c r="J51" s="32">
+      <c r="J51" s="33">
         <v>8.42</v>
       </c>
-      <c r="K51" s="32">
+      <c r="K51" s="33">
         <v>7.56</v>
       </c>
-      <c r="L51" s="32">
+      <c r="L51" s="33">
         <v>7.21</v>
       </c>
-      <c r="M51" s="32">
+      <c r="M51" s="33">
         <v>6.61</v>
       </c>
-      <c r="N51" s="32">
+      <c r="N51" s="33">
         <v>5.81</v>
       </c>
-      <c r="O51" s="32">
+      <c r="O51" s="33">
         <v>7.19</v>
       </c>
-      <c r="P51" s="32">
+      <c r="P51" s="33">
         <v>8.5</v>
       </c>
-      <c r="Q51" s="32">
+      <c r="Q51" s="33">
         <v>8.96</v>
       </c>
-      <c r="R51" s="32">
+      <c r="R51" s="33">
         <v>9.28</v>
       </c>
-      <c r="S51" s="32">
+      <c r="S51" s="33">
         <v>8.3</v>
       </c>
-      <c r="T51" s="32">
+      <c r="T51" s="33">
         <v>5.96</v>
       </c>
-      <c r="U51" s="32">
+      <c r="U51" s="33">
         <v>4.54</v>
       </c>
-      <c r="V51" s="32">
+      <c r="V51" s="33">
         <v>3.2</v>
       </c>
-      <c r="W51" s="32">
+      <c r="W51" s="33">
         <v>2.78</v>
       </c>
-      <c r="X51" s="32">
+      <c r="X51" s="33">
         <v>2.61</v>
       </c>
-      <c r="Y51" s="32">
+      <c r="Y51" s="33">
         <v>2.69</v>
       </c>
-      <c r="Z51" s="32">
+      <c r="Z51" s="33">
         <v>1.61</v>
       </c>
-      <c r="AA51" s="31"/>
-      <c r="AB51" s="31"/>
-      <c r="AC51" s="31"/>
-      <c r="AD51" s="31"/>
+      <c r="AA51" s="32"/>
+      <c r="AB51" s="32"/>
+      <c r="AC51" s="32"/>
+      <c r="AD51" s="32"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="27" t="s">
-        <v>528</v>
-      </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="28"/>
-      <c r="O52" s="28"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="28"/>
-      <c r="R52" s="28"/>
-      <c r="S52" s="28"/>
-      <c r="T52" s="28"/>
-      <c r="U52" s="28"/>
-      <c r="V52" s="28"/>
-      <c r="W52" s="28"/>
-      <c r="X52" s="28"/>
-      <c r="Y52" s="28"/>
-      <c r="Z52" s="28"/>
-      <c r="AA52" s="28"/>
-      <c r="AB52" s="28"/>
-      <c r="AC52" s="28"/>
-      <c r="AD52" s="28"/>
+      <c r="A52" s="28" t="s">
+        <v>529</v>
+      </c>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="29"/>
+      <c r="N52" s="29"/>
+      <c r="O52" s="29"/>
+      <c r="P52" s="29"/>
+      <c r="Q52" s="29"/>
+      <c r="R52" s="29"/>
+      <c r="S52" s="29"/>
+      <c r="T52" s="29"/>
+      <c r="U52" s="29"/>
+      <c r="V52" s="29"/>
+      <c r="W52" s="29"/>
+      <c r="X52" s="29"/>
+      <c r="Y52" s="29"/>
+      <c r="Z52" s="29"/>
+      <c r="AA52" s="29"/>
+      <c r="AB52" s="29"/>
+      <c r="AC52" s="29"/>
+      <c r="AD52" s="29"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="29" t="s">
-        <v>529</v>
-      </c>
-      <c r="B53" s="31"/>
-      <c r="C53" s="32">
+      <c r="A53" s="30" t="s">
+        <v>530</v>
+      </c>
+      <c r="B53" s="32"/>
+      <c r="C53" s="33">
         <v>2.94</v>
       </c>
-      <c r="D53" s="32">
+      <c r="D53" s="33">
         <v>2.93</v>
       </c>
-      <c r="E53" s="32">
+      <c r="E53" s="33">
         <v>14.89</v>
       </c>
-      <c r="F53" s="32">
+      <c r="F53" s="33">
         <v>30.04</v>
       </c>
-      <c r="G53" s="32">
+      <c r="G53" s="33">
         <v>17.42</v>
       </c>
-      <c r="H53" s="32">
+      <c r="H53" s="33">
         <v>16.85</v>
       </c>
-      <c r="I53" s="32">
+      <c r="I53" s="33">
         <v>20.64</v>
       </c>
-      <c r="J53" s="32">
+      <c r="J53" s="33">
         <v>16.98</v>
       </c>
-      <c r="K53" s="32">
+      <c r="K53" s="33">
         <v>18.34</v>
       </c>
-      <c r="L53" s="32">
+      <c r="L53" s="33">
         <v>32.4</v>
       </c>
-      <c r="M53" s="32">
+      <c r="M53" s="33">
         <v>26.58</v>
       </c>
-      <c r="N53" s="32">
+      <c r="N53" s="33">
         <v>12.35</v>
       </c>
-      <c r="O53" s="32">
+      <c r="O53" s="33">
         <v>23.65</v>
       </c>
-      <c r="P53" s="32">
+      <c r="P53" s="33">
         <v>19.2</v>
       </c>
-      <c r="Q53" s="32">
+      <c r="Q53" s="33">
         <v>16.85</v>
       </c>
-      <c r="R53" s="32">
+      <c r="R53" s="33">
         <v>9.62</v>
       </c>
-      <c r="S53" s="32">
+      <c r="S53" s="33">
         <v>24.89</v>
       </c>
-      <c r="T53" s="32">
+      <c r="T53" s="33">
         <v>21.75</v>
       </c>
-      <c r="U53" s="32">
+      <c r="U53" s="33">
         <v>19.22</v>
       </c>
-      <c r="V53" s="32">
+      <c r="V53" s="33">
         <v>11.74</v>
       </c>
-      <c r="W53" s="32">
+      <c r="W53" s="33">
         <v>7.05</v>
       </c>
-      <c r="X53" s="32">
+      <c r="X53" s="33">
         <v>5.46</v>
       </c>
-      <c r="Y53" s="32">
+      <c r="Y53" s="33">
         <v>6.78</v>
       </c>
-      <c r="Z53" s="32">
+      <c r="Z53" s="33">
         <v>4.62</v>
       </c>
-      <c r="AA53" s="32">
+      <c r="AA53" s="33">
         <v>5.59</v>
       </c>
-      <c r="AB53" s="32">
+      <c r="AB53" s="33">
         <v>4.55</v>
       </c>
-      <c r="AC53" s="32">
+      <c r="AC53" s="33">
         <v>5.13</v>
       </c>
-      <c r="AD53" s="32">
+      <c r="AD53" s="33">
         <v>0.88</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="29" t="s">
-        <v>530</v>
-      </c>
-      <c r="B54" s="32">
+      <c r="A54" s="30" t="s">
+        <v>531</v>
+      </c>
+      <c r="B54" s="33">
         <v>4.39</v>
       </c>
-      <c r="C54" s="32">
+      <c r="C54" s="33">
         <v>3.78</v>
       </c>
-      <c r="D54" s="32">
+      <c r="D54" s="33">
         <v>3.96</v>
       </c>
-      <c r="E54" s="32">
+      <c r="E54" s="33">
         <v>18.98</v>
       </c>
-      <c r="F54" s="32">
+      <c r="F54" s="33">
         <v>19.31</v>
       </c>
-      <c r="G54" s="32">
+      <c r="G54" s="33">
         <v>17.99</v>
       </c>
-      <c r="H54" s="32">
+      <c r="H54" s="33">
         <v>19.66</v>
       </c>
-      <c r="I54" s="32">
+      <c r="I54" s="33">
         <v>21.26</v>
       </c>
-      <c r="J54" s="32">
+      <c r="J54" s="33">
         <v>19.43</v>
       </c>
-      <c r="K54" s="32">
+      <c r="K54" s="33">
         <v>20.81</v>
       </c>
-      <c r="L54" s="32">
+      <c r="L54" s="33">
         <v>21.24</v>
       </c>
-      <c r="M54" s="32">
+      <c r="M54" s="33">
         <v>18.64</v>
       </c>
-      <c r="N54" s="32">
+      <c r="N54" s="33">
         <v>15.1</v>
       </c>
-      <c r="O54" s="32">
+      <c r="O54" s="33">
         <v>17.83</v>
       </c>
-      <c r="P54" s="32">
+      <c r="P54" s="33">
         <v>18.06</v>
       </c>
-      <c r="Q54" s="32">
+      <c r="Q54" s="33">
         <v>18.06</v>
       </c>
-      <c r="R54" s="32">
+      <c r="R54" s="33">
         <v>16.86</v>
       </c>
-      <c r="S54" s="32">
+      <c r="S54" s="33">
         <v>15.6</v>
       </c>
-      <c r="T54" s="32">
+      <c r="T54" s="33">
         <v>12.03</v>
       </c>
-      <c r="U54" s="32">
+      <c r="U54" s="33">
         <v>9.31</v>
       </c>
-      <c r="V54" s="32">
+      <c r="V54" s="33">
         <v>6.95</v>
       </c>
-      <c r="W54" s="32">
+      <c r="W54" s="33">
         <v>5.85</v>
       </c>
-      <c r="X54" s="32">
+      <c r="X54" s="33">
         <v>5.27</v>
       </c>
-      <c r="Y54" s="32">
+      <c r="Y54" s="33">
         <v>5.22</v>
       </c>
-      <c r="Z54" s="32">
+      <c r="Z54" s="33">
         <v>3.14</v>
       </c>
-      <c r="AA54" s="31"/>
-      <c r="AB54" s="31"/>
-      <c r="AC54" s="31"/>
-      <c r="AD54" s="31"/>
+      <c r="AA54" s="32"/>
+      <c r="AB54" s="32"/>
+      <c r="AC54" s="32"/>
+      <c r="AD54" s="32"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="27" t="s">
-        <v>531</v>
-      </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
-      <c r="J55" s="28"/>
-      <c r="K55" s="28"/>
-      <c r="L55" s="28"/>
-      <c r="M55" s="28"/>
-      <c r="N55" s="28"/>
-      <c r="O55" s="28"/>
-      <c r="P55" s="28"/>
-      <c r="Q55" s="28"/>
-      <c r="R55" s="28"/>
-      <c r="S55" s="28"/>
-      <c r="T55" s="28"/>
-      <c r="U55" s="28"/>
-      <c r="V55" s="28"/>
-      <c r="W55" s="28"/>
-      <c r="X55" s="28"/>
-      <c r="Y55" s="28"/>
-      <c r="Z55" s="28"/>
-      <c r="AA55" s="28"/>
-      <c r="AB55" s="28"/>
-      <c r="AC55" s="28"/>
-      <c r="AD55" s="28"/>
+      <c r="A55" s="28" t="s">
+        <v>532</v>
+      </c>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="29"/>
+      <c r="M55" s="29"/>
+      <c r="N55" s="29"/>
+      <c r="O55" s="29"/>
+      <c r="P55" s="29"/>
+      <c r="Q55" s="29"/>
+      <c r="R55" s="29"/>
+      <c r="S55" s="29"/>
+      <c r="T55" s="29"/>
+      <c r="U55" s="29"/>
+      <c r="V55" s="29"/>
+      <c r="W55" s="29"/>
+      <c r="X55" s="29"/>
+      <c r="Y55" s="29"/>
+      <c r="Z55" s="29"/>
+      <c r="AA55" s="29"/>
+      <c r="AB55" s="29"/>
+      <c r="AC55" s="29"/>
+      <c r="AD55" s="29"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="29" t="s">
-        <v>532</v>
-      </c>
-      <c r="B56" s="32">
+      <c r="A56" s="30" t="s">
+        <v>533</v>
+      </c>
+      <c r="B56" s="33">
         <v>2.49</v>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="33">
         <v>2.82</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="33">
         <v>3.77</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="33">
         <v>14.8</v>
       </c>
-      <c r="F56" s="32">
+      <c r="F56" s="33">
         <v>20.42</v>
       </c>
-      <c r="G56" s="32">
+      <c r="G56" s="33">
         <v>17.42</v>
       </c>
-      <c r="H56" s="32">
+      <c r="H56" s="33">
         <v>16.85</v>
       </c>
-      <c r="I56" s="32">
+      <c r="I56" s="33">
         <v>20.7</v>
       </c>
-      <c r="J56" s="32">
+      <c r="J56" s="33">
         <v>16.98</v>
       </c>
-      <c r="K56" s="32">
+      <c r="K56" s="33">
         <v>19.69</v>
       </c>
-      <c r="L56" s="32">
+      <c r="L56" s="33">
         <v>25.72</v>
       </c>
-      <c r="M56" s="32">
+      <c r="M56" s="33">
         <v>14.24</v>
       </c>
-      <c r="N56" s="32">
+      <c r="N56" s="33">
         <v>13.24</v>
       </c>
-      <c r="O56" s="32">
+      <c r="O56" s="33">
         <v>11.29</v>
       </c>
-      <c r="P56" s="32">
+      <c r="P56" s="33">
         <v>17.84</v>
       </c>
-      <c r="Q56" s="32">
+      <c r="Q56" s="33">
         <v>12.3</v>
       </c>
-      <c r="R56" s="32">
+      <c r="R56" s="33">
         <v>8.93</v>
       </c>
-      <c r="S56" s="32">
+      <c r="S56" s="33">
         <v>42.1</v>
       </c>
-      <c r="T56" s="32">
+      <c r="T56" s="33">
         <v>21.75</v>
       </c>
-      <c r="U56" s="32">
+      <c r="U56" s="33">
         <v>19.22</v>
       </c>
-      <c r="V56" s="32">
+      <c r="V56" s="33">
         <v>11.74</v>
       </c>
-      <c r="W56" s="32">
+      <c r="W56" s="33">
         <v>5.2</v>
       </c>
-      <c r="X56" s="32">
+      <c r="X56" s="33">
         <v>3.98</v>
       </c>
-      <c r="Y56" s="32">
+      <c r="Y56" s="33">
         <v>7.36</v>
       </c>
-      <c r="Z56" s="32">
+      <c r="Z56" s="33">
         <v>4.19</v>
       </c>
-      <c r="AA56" s="32">
+      <c r="AA56" s="33">
         <v>9.95</v>
       </c>
-      <c r="AB56" s="32">
+      <c r="AB56" s="33">
         <v>4.51</v>
       </c>
-      <c r="AC56" s="32">
+      <c r="AC56" s="33">
         <v>5.05</v>
       </c>
-      <c r="AD56" s="32">
+      <c r="AD56" s="33">
         <v>0.87</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="29" t="s">
-        <v>533</v>
-      </c>
-      <c r="B57" s="32">
+      <c r="A57" s="30" t="s">
+        <v>534</v>
+      </c>
+      <c r="B57" s="33">
         <v>0.46</v>
       </c>
-      <c r="C57" s="32">
+      <c r="C57" s="33">
         <v>0.53</v>
       </c>
-      <c r="D57" s="32">
+      <c r="D57" s="33">
         <v>0.59</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="33">
         <v>2.85</v>
       </c>
-      <c r="F57" s="32">
+      <c r="F57" s="33">
         <v>3.03</v>
       </c>
-      <c r="G57" s="32">
+      <c r="G57" s="33">
         <v>3.09</v>
       </c>
-      <c r="H57" s="32">
+      <c r="H57" s="33">
         <v>3.07</v>
       </c>
-      <c r="I57" s="32">
+      <c r="I57" s="33">
         <v>3.09</v>
       </c>
-      <c r="J57" s="32">
+      <c r="J57" s="33">
         <v>2.8</v>
       </c>
-      <c r="K57" s="32">
+      <c r="K57" s="33">
         <v>2.5</v>
       </c>
-      <c r="L57" s="32">
+      <c r="L57" s="33">
         <v>2.31</v>
       </c>
-      <c r="M57" s="32">
+      <c r="M57" s="33">
         <v>2.26</v>
       </c>
-      <c r="N57" s="32">
+      <c r="N57" s="33">
         <v>2.08</v>
       </c>
-      <c r="O57" s="32">
+      <c r="O57" s="33">
         <v>2.49</v>
       </c>
-      <c r="P57" s="32">
+      <c r="P57" s="33">
         <v>2.94</v>
       </c>
-      <c r="Q57" s="32">
+      <c r="Q57" s="33">
         <v>3.16</v>
       </c>
-      <c r="R57" s="32">
+      <c r="R57" s="33">
         <v>3.34</v>
       </c>
-      <c r="S57" s="32">
+      <c r="S57" s="33">
         <v>3.83</v>
       </c>
-      <c r="T57" s="32">
+      <c r="T57" s="33">
         <v>3.63</v>
       </c>
-      <c r="U57" s="32">
+      <c r="U57" s="33">
         <v>3.35</v>
       </c>
-      <c r="V57" s="32">
+      <c r="V57" s="33">
         <v>3.0</v>
       </c>
-      <c r="W57" s="32">
+      <c r="W57" s="33">
         <v>2.82</v>
       </c>
-      <c r="X57" s="32">
+      <c r="X57" s="33">
         <v>1.89</v>
       </c>
-      <c r="Y57" s="32">
+      <c r="Y57" s="33">
         <v>1.58</v>
       </c>
-      <c r="Z57" s="32">
+      <c r="Z57" s="33">
         <v>0.79</v>
       </c>
-      <c r="AA57" s="31"/>
-      <c r="AB57" s="31"/>
-      <c r="AC57" s="31"/>
-      <c r="AD57" s="31"/>
+      <c r="AA57" s="32"/>
+      <c r="AB57" s="32"/>
+      <c r="AC57" s="32"/>
+      <c r="AD57" s="32"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="27" t="s">
-        <v>534</v>
-      </c>
-      <c r="B58" s="28"/>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28"/>
-      <c r="J58" s="28"/>
-      <c r="K58" s="28"/>
-      <c r="L58" s="28"/>
-      <c r="M58" s="28"/>
-      <c r="N58" s="28"/>
-      <c r="O58" s="28"/>
-      <c r="P58" s="28"/>
-      <c r="Q58" s="28"/>
-      <c r="R58" s="28"/>
-      <c r="S58" s="28"/>
-      <c r="T58" s="28"/>
-      <c r="U58" s="28"/>
-      <c r="V58" s="28"/>
-      <c r="W58" s="28"/>
-      <c r="X58" s="28"/>
-      <c r="Y58" s="28"/>
-      <c r="Z58" s="28"/>
-      <c r="AA58" s="28"/>
-      <c r="AB58" s="28"/>
-      <c r="AC58" s="28"/>
-      <c r="AD58" s="28"/>
+      <c r="A58" s="28" t="s">
+        <v>535</v>
+      </c>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="29"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="29"/>
+      <c r="L58" s="29"/>
+      <c r="M58" s="29"/>
+      <c r="N58" s="29"/>
+      <c r="O58" s="29"/>
+      <c r="P58" s="29"/>
+      <c r="Q58" s="29"/>
+      <c r="R58" s="29"/>
+      <c r="S58" s="29"/>
+      <c r="T58" s="29"/>
+      <c r="U58" s="29"/>
+      <c r="V58" s="29"/>
+      <c r="W58" s="29"/>
+      <c r="X58" s="29"/>
+      <c r="Y58" s="29"/>
+      <c r="Z58" s="29"/>
+      <c r="AA58" s="29"/>
+      <c r="AB58" s="29"/>
+      <c r="AC58" s="29"/>
+      <c r="AD58" s="29"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="29" t="s">
-        <v>535</v>
-      </c>
-      <c r="B59" s="31"/>
-      <c r="C59" s="35">
+      <c r="A59" s="30" t="s">
+        <v>536</v>
+      </c>
+      <c r="B59" s="32"/>
+      <c r="C59" s="36">
         <v>-0.37</v>
       </c>
-      <c r="D59" s="35">
+      <c r="D59" s="36">
         <v>-0.35</v>
       </c>
-      <c r="E59" s="32">
+      <c r="E59" s="33">
         <v>0.19</v>
       </c>
-      <c r="F59" s="35">
+      <c r="F59" s="36">
         <v>-0.67</v>
       </c>
-      <c r="G59" s="32">
+      <c r="G59" s="33">
         <v>9.9</v>
       </c>
-      <c r="H59" s="32">
+      <c r="H59" s="33">
         <v>11.32</v>
       </c>
-      <c r="I59" s="35">
+      <c r="I59" s="36">
         <v>-0.91</v>
       </c>
-      <c r="J59" s="32">
+      <c r="J59" s="33">
         <v>1.18</v>
       </c>
-      <c r="K59" s="32">
+      <c r="K59" s="33">
         <v>0.16</v>
       </c>
-      <c r="L59" s="35">
+      <c r="L59" s="36">
         <v>-1.76</v>
       </c>
-      <c r="M59" s="35">
+      <c r="M59" s="36">
         <v>-0.75</v>
       </c>
-      <c r="N59" s="32">
+      <c r="N59" s="33">
         <v>0.12</v>
       </c>
-      <c r="O59" s="35">
+      <c r="O59" s="36">
         <v>-0.65</v>
       </c>
-      <c r="P59" s="35">
+      <c r="P59" s="36">
         <v>-1.0</v>
       </c>
-      <c r="Q59" s="35">
+      <c r="Q59" s="36">
         <v>-0.99</v>
       </c>
-      <c r="R59" s="32">
+      <c r="R59" s="33">
         <v>0.38</v>
       </c>
-      <c r="S59" s="35">
+      <c r="S59" s="36">
         <v>-2.97</v>
       </c>
-      <c r="T59" s="32">
+      <c r="T59" s="33">
         <v>0.76</v>
       </c>
-      <c r="U59" s="35">
+      <c r="U59" s="36">
         <v>-0.63</v>
       </c>
-      <c r="V59" s="35">
+      <c r="V59" s="36">
         <v>-0.44</v>
       </c>
-      <c r="W59" s="32">
+      <c r="W59" s="33">
         <v>0.19</v>
       </c>
-      <c r="X59" s="32">
+      <c r="X59" s="33">
         <v>0.78</v>
       </c>
-      <c r="Y59" s="35">
+      <c r="Y59" s="36">
         <v>-0.2</v>
       </c>
-      <c r="Z59" s="35">
+      <c r="Z59" s="36">
         <v>-0.57</v>
       </c>
-      <c r="AA59" s="35">
+      <c r="AA59" s="36">
         <v>-1.09</v>
       </c>
-      <c r="AB59" s="32">
+      <c r="AB59" s="33">
         <v>0.4</v>
       </c>
-      <c r="AC59" s="35">
+      <c r="AC59" s="36">
         <v>-0.07</v>
       </c>
-      <c r="AD59" s="31"/>
+      <c r="AD59" s="32"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="29" t="s">
-        <v>536</v>
-      </c>
-      <c r="B60" s="31"/>
-      <c r="C60" s="35">
+      <c r="A60" s="30" t="s">
+        <v>537</v>
+      </c>
+      <c r="B60" s="32"/>
+      <c r="C60" s="36">
         <v>-1.23</v>
       </c>
-      <c r="D60" s="35">
+      <c r="D60" s="36">
         <v>-3.48</v>
       </c>
-      <c r="E60" s="35">
+      <c r="E60" s="36">
         <v>-4.31</v>
       </c>
-      <c r="F60" s="35">
+      <c r="F60" s="36">
         <v>-1.52</v>
       </c>
-      <c r="G60" s="32">
+      <c r="G60" s="33">
         <v>1.28</v>
       </c>
-      <c r="H60" s="32">
+      <c r="H60" s="33">
         <v>2.15</v>
       </c>
-      <c r="I60" s="35">
+      <c r="I60" s="36">
         <v>-61.07</v>
       </c>
-      <c r="J60" s="32">
+      <c r="J60" s="33">
         <v>0.93</v>
       </c>
-      <c r="K60" s="32">
+      <c r="K60" s="33">
         <v>2.81</v>
       </c>
-      <c r="L60" s="35">
+      <c r="L60" s="36">
         <v>-1.87</v>
       </c>
-      <c r="M60" s="35">
+      <c r="M60" s="36">
         <v>-1.69</v>
       </c>
-      <c r="N60" s="32">
+      <c r="N60" s="33">
         <v>9.3</v>
       </c>
-      <c r="O60" s="35">
+      <c r="O60" s="36">
         <v>-1.33</v>
       </c>
-      <c r="P60" s="35">
+      <c r="P60" s="36">
         <v>-86.34</v>
       </c>
-      <c r="Q60" s="35">
+      <c r="Q60" s="36">
         <v>-5.58</v>
       </c>
-      <c r="R60" s="35">
+      <c r="R60" s="36">
         <v>-2.97</v>
       </c>
-      <c r="S60" s="35">
+      <c r="S60" s="36">
         <v>-3.97</v>
       </c>
-      <c r="T60" s="35">
+      <c r="T60" s="36">
         <v>-13.44</v>
       </c>
-      <c r="U60" s="35">
+      <c r="U60" s="36">
         <v>-0.7</v>
       </c>
-      <c r="V60" s="35">
+      <c r="V60" s="36">
         <v>-0.84</v>
       </c>
-      <c r="W60" s="35">
+      <c r="W60" s="36">
         <v>-1.76</v>
       </c>
-      <c r="X60" s="35">
+      <c r="X60" s="36">
         <v>-0.72</v>
       </c>
-      <c r="Y60" s="35">
+      <c r="Y60" s="36">
         <v>-0.18</v>
       </c>
-      <c r="Z60" s="31"/>
-      <c r="AA60" s="31"/>
-      <c r="AB60" s="31"/>
-      <c r="AC60" s="31"/>
-      <c r="AD60" s="31"/>
+      <c r="Z60" s="32"/>
+      <c r="AA60" s="32"/>
+      <c r="AB60" s="32"/>
+      <c r="AC60" s="32"/>
+      <c r="AD60" s="32"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="27" t="s">
-        <v>537</v>
-      </c>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="28"/>
-      <c r="J61" s="28"/>
-      <c r="K61" s="28"/>
-      <c r="L61" s="28"/>
-      <c r="M61" s="28"/>
-      <c r="N61" s="28"/>
-      <c r="O61" s="28"/>
-      <c r="P61" s="28"/>
-      <c r="Q61" s="28"/>
-      <c r="R61" s="28"/>
-      <c r="S61" s="28"/>
-      <c r="T61" s="28"/>
-      <c r="U61" s="28"/>
-      <c r="V61" s="28"/>
-      <c r="W61" s="28"/>
-      <c r="X61" s="28"/>
-      <c r="Y61" s="28"/>
-      <c r="Z61" s="28"/>
-      <c r="AA61" s="28"/>
-      <c r="AB61" s="28"/>
-      <c r="AC61" s="28"/>
-      <c r="AD61" s="28"/>
+      <c r="A61" s="28" t="s">
+        <v>538</v>
+      </c>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
+      <c r="E61" s="29"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="29"/>
+      <c r="H61" s="29"/>
+      <c r="I61" s="29"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
+      <c r="L61" s="29"/>
+      <c r="M61" s="29"/>
+      <c r="N61" s="29"/>
+      <c r="O61" s="29"/>
+      <c r="P61" s="29"/>
+      <c r="Q61" s="29"/>
+      <c r="R61" s="29"/>
+      <c r="S61" s="29"/>
+      <c r="T61" s="29"/>
+      <c r="U61" s="29"/>
+      <c r="V61" s="29"/>
+      <c r="W61" s="29"/>
+      <c r="X61" s="29"/>
+      <c r="Y61" s="29"/>
+      <c r="Z61" s="29"/>
+      <c r="AA61" s="29"/>
+      <c r="AB61" s="29"/>
+      <c r="AC61" s="29"/>
+      <c r="AD61" s="29"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="29" t="s">
-        <v>538</v>
-      </c>
-      <c r="B62" s="32">
+      <c r="A62" s="30" t="s">
+        <v>539</v>
+      </c>
+      <c r="B62" s="33">
         <v>0.29</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="33">
         <v>0.31</v>
       </c>
-      <c r="D62" s="32">
+      <c r="D62" s="33">
         <v>0.31</v>
       </c>
-      <c r="E62" s="32">
+      <c r="E62" s="33">
         <v>0.85</v>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="33">
         <v>0.96</v>
       </c>
-      <c r="G62" s="32">
+      <c r="G62" s="33">
         <v>0.95</v>
       </c>
-      <c r="H62" s="32">
+      <c r="H62" s="33">
         <v>0.85</v>
       </c>
-      <c r="I62" s="32">
+      <c r="I62" s="33">
         <v>1.15</v>
       </c>
-      <c r="J62" s="32">
+      <c r="J62" s="33">
         <v>1.18</v>
       </c>
-      <c r="K62" s="32">
+      <c r="K62" s="33">
         <v>1.15</v>
       </c>
-      <c r="L62" s="32">
+      <c r="L62" s="33">
         <v>1.0</v>
       </c>
-      <c r="M62" s="32">
+      <c r="M62" s="33">
         <v>0.98</v>
       </c>
-      <c r="N62" s="32">
+      <c r="N62" s="33">
         <v>0.76</v>
       </c>
-      <c r="O62" s="32">
+      <c r="O62" s="33">
         <v>0.81</v>
       </c>
-      <c r="P62" s="32">
+      <c r="P62" s="33">
         <v>1.05</v>
       </c>
-      <c r="Q62" s="32">
+      <c r="Q62" s="33">
         <v>1.16</v>
       </c>
-      <c r="R62" s="32">
+      <c r="R62" s="33">
         <v>0.83</v>
       </c>
-      <c r="S62" s="32">
+      <c r="S62" s="33">
         <v>1.59</v>
       </c>
-      <c r="T62" s="32">
+      <c r="T62" s="33">
         <v>1.81</v>
       </c>
-      <c r="U62" s="32">
+      <c r="U62" s="33">
         <v>1.57</v>
       </c>
-      <c r="V62" s="32">
+      <c r="V62" s="33">
         <v>1.52</v>
       </c>
-      <c r="W62" s="32">
+      <c r="W62" s="33">
         <v>1.54</v>
       </c>
-      <c r="X62" s="32">
+      <c r="X62" s="33">
         <v>1.1</v>
       </c>
-      <c r="Y62" s="32">
+      <c r="Y62" s="33">
         <v>1.34</v>
       </c>
-      <c r="Z62" s="32">
+      <c r="Z62" s="33">
         <v>0.98</v>
       </c>
-      <c r="AA62" s="32">
+      <c r="AA62" s="33">
         <v>1.19</v>
       </c>
-      <c r="AB62" s="32">
+      <c r="AB62" s="33">
         <v>0.41</v>
       </c>
-      <c r="AC62" s="32">
+      <c r="AC62" s="33">
         <v>0.4</v>
       </c>
-      <c r="AD62" s="32">
+      <c r="AD62" s="33">
         <v>0.07</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="29" t="s">
-        <v>539</v>
-      </c>
-      <c r="B63" s="32">
+      <c r="A63" s="30" t="s">
+        <v>540</v>
+      </c>
+      <c r="B63" s="33">
         <v>0.54</v>
       </c>
-      <c r="C63" s="32">
+      <c r="C63" s="33">
         <v>0.67</v>
       </c>
-      <c r="D63" s="32">
+      <c r="D63" s="33">
         <v>0.77</v>
       </c>
-      <c r="E63" s="32">
+      <c r="E63" s="33">
         <v>0.95</v>
       </c>
-      <c r="F63" s="32">
+      <c r="F63" s="33">
         <v>1.01</v>
       </c>
-      <c r="G63" s="32">
+      <c r="G63" s="33">
         <v>1.05</v>
       </c>
-      <c r="H63" s="32">
+      <c r="H63" s="33">
         <v>1.06</v>
       </c>
-      <c r="I63" s="32">
+      <c r="I63" s="33">
         <v>1.1</v>
       </c>
-      <c r="J63" s="32">
+      <c r="J63" s="33">
         <v>1.01</v>
       </c>
-      <c r="K63" s="32">
+      <c r="K63" s="33">
         <v>0.94</v>
       </c>
-      <c r="L63" s="32">
+      <c r="L63" s="33">
         <v>0.92</v>
       </c>
-      <c r="M63" s="32">
+      <c r="M63" s="33">
         <v>0.94</v>
       </c>
-      <c r="N63" s="32">
+      <c r="N63" s="33">
         <v>0.91</v>
       </c>
-      <c r="O63" s="32">
+      <c r="O63" s="33">
         <v>1.07</v>
       </c>
-      <c r="P63" s="32">
+      <c r="P63" s="33">
         <v>1.25</v>
       </c>
-      <c r="Q63" s="32">
+      <c r="Q63" s="33">
         <v>1.35</v>
       </c>
-      <c r="R63" s="32">
+      <c r="R63" s="33">
         <v>1.42</v>
       </c>
-      <c r="S63" s="32">
+      <c r="S63" s="33">
         <v>1.61</v>
       </c>
-      <c r="T63" s="32">
+      <c r="T63" s="33">
         <v>1.54</v>
       </c>
-      <c r="U63" s="32">
+      <c r="U63" s="33">
         <v>1.44</v>
       </c>
-      <c r="V63" s="32">
+      <c r="V63" s="33">
         <v>1.29</v>
       </c>
-      <c r="W63" s="32">
+      <c r="W63" s="33">
         <v>1.21</v>
       </c>
-      <c r="X63" s="32">
+      <c r="X63" s="33">
         <v>0.99</v>
       </c>
-      <c r="Y63" s="32">
+      <c r="Y63" s="33">
         <v>0.87</v>
       </c>
-      <c r="Z63" s="32">
+      <c r="Z63" s="33">
         <v>0.66</v>
       </c>
-      <c r="AA63" s="31"/>
-      <c r="AB63" s="31"/>
-      <c r="AC63" s="31"/>
-      <c r="AD63" s="31"/>
+      <c r="AA63" s="32"/>
+      <c r="AB63" s="32"/>
+      <c r="AC63" s="32"/>
+      <c r="AD63" s="32"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="27" t="s">
-        <v>540</v>
-      </c>
-      <c r="B64" s="28"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="28"/>
-      <c r="F64" s="28"/>
-      <c r="G64" s="28"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="28"/>
-      <c r="J64" s="28"/>
-      <c r="K64" s="28"/>
-      <c r="L64" s="28"/>
-      <c r="M64" s="28"/>
-      <c r="N64" s="28"/>
-      <c r="O64" s="28"/>
-      <c r="P64" s="28"/>
-      <c r="Q64" s="28"/>
-      <c r="R64" s="28"/>
-      <c r="S64" s="28"/>
-      <c r="T64" s="28"/>
-      <c r="U64" s="28"/>
-      <c r="V64" s="28"/>
-      <c r="W64" s="28"/>
-      <c r="X64" s="28"/>
-      <c r="Y64" s="28"/>
-      <c r="Z64" s="28"/>
-      <c r="AA64" s="28"/>
-      <c r="AB64" s="28"/>
-      <c r="AC64" s="28"/>
-      <c r="AD64" s="28"/>
+      <c r="A64" s="28" t="s">
+        <v>541</v>
+      </c>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+      <c r="D64" s="29"/>
+      <c r="E64" s="29"/>
+      <c r="F64" s="29"/>
+      <c r="G64" s="29"/>
+      <c r="H64" s="29"/>
+      <c r="I64" s="29"/>
+      <c r="J64" s="29"/>
+      <c r="K64" s="29"/>
+      <c r="L64" s="29"/>
+      <c r="M64" s="29"/>
+      <c r="N64" s="29"/>
+      <c r="O64" s="29"/>
+      <c r="P64" s="29"/>
+      <c r="Q64" s="29"/>
+      <c r="R64" s="29"/>
+      <c r="S64" s="29"/>
+      <c r="T64" s="29"/>
+      <c r="U64" s="29"/>
+      <c r="V64" s="29"/>
+      <c r="W64" s="29"/>
+      <c r="X64" s="29"/>
+      <c r="Y64" s="29"/>
+      <c r="Z64" s="29"/>
+      <c r="AA64" s="29"/>
+      <c r="AB64" s="29"/>
+      <c r="AC64" s="29"/>
+      <c r="AD64" s="29"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="29" t="s">
-        <v>541</v>
-      </c>
-      <c r="B65" s="32">
+      <c r="A65" s="30" t="s">
+        <v>542</v>
+      </c>
+      <c r="B65" s="33">
         <v>2.38</v>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="33">
         <v>2.61</v>
       </c>
-      <c r="D65" s="32">
+      <c r="D65" s="33">
         <v>2.92</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65" s="33">
         <v>7.38</v>
       </c>
-      <c r="F65" s="32">
+      <c r="F65" s="33">
         <v>8.32</v>
       </c>
-      <c r="G65" s="32">
+      <c r="G65" s="33">
         <v>9.1</v>
       </c>
-      <c r="H65" s="32">
+      <c r="H65" s="33">
         <v>7.67</v>
       </c>
-      <c r="I65" s="32">
+      <c r="I65" s="33">
         <v>9.82</v>
       </c>
-      <c r="J65" s="32">
+      <c r="J65" s="33">
         <v>8.78</v>
       </c>
-      <c r="K65" s="32">
+      <c r="K65" s="33">
         <v>8.58</v>
       </c>
-      <c r="L65" s="32">
+      <c r="L65" s="33">
         <v>7.53</v>
       </c>
-      <c r="M65" s="32">
+      <c r="M65" s="33">
         <v>7.63</v>
       </c>
-      <c r="N65" s="32">
+      <c r="N65" s="33">
         <v>5.88</v>
       </c>
-      <c r="O65" s="32">
+      <c r="O65" s="33">
         <v>5.09</v>
       </c>
-      <c r="P65" s="32">
+      <c r="P65" s="33">
         <v>7.24</v>
       </c>
-      <c r="Q65" s="32">
+      <c r="Q65" s="33">
         <v>7.44</v>
       </c>
-      <c r="R65" s="32">
+      <c r="R65" s="33">
         <v>5.07</v>
       </c>
-      <c r="S65" s="32">
+      <c r="S65" s="33">
         <v>10.82</v>
       </c>
-      <c r="T65" s="32">
+      <c r="T65" s="33">
         <v>10.07</v>
       </c>
-      <c r="U65" s="32">
+      <c r="U65" s="33">
         <v>9.27</v>
       </c>
-      <c r="V65" s="32">
+      <c r="V65" s="33">
         <v>7.07</v>
       </c>
-      <c r="W65" s="32">
+      <c r="W65" s="33">
         <v>6.81</v>
       </c>
-      <c r="X65" s="32">
+      <c r="X65" s="33">
         <v>5.37</v>
       </c>
-      <c r="Y65" s="32">
+      <c r="Y65" s="33">
         <v>6.12</v>
       </c>
-      <c r="Z65" s="31"/>
-      <c r="AA65" s="32">
+      <c r="Z65" s="32"/>
+      <c r="AA65" s="33">
         <v>6.05</v>
       </c>
-      <c r="AB65" s="32">
+      <c r="AB65" s="33">
         <v>2.16</v>
       </c>
-      <c r="AC65" s="32">
+      <c r="AC65" s="33">
         <v>2.04</v>
       </c>
-      <c r="AD65" s="32">
+      <c r="AD65" s="33">
         <v>0.38</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="29" t="s">
-        <v>542</v>
-      </c>
-      <c r="B66" s="32">
+      <c r="A66" s="30" t="s">
+        <v>543</v>
+      </c>
+      <c r="B66" s="33">
         <v>4.67</v>
       </c>
-      <c r="C66" s="32">
+      <c r="C66" s="33">
         <v>5.97</v>
       </c>
-      <c r="D66" s="32">
+      <c r="D66" s="33">
         <v>7.04</v>
       </c>
-      <c r="E66" s="32">
+      <c r="E66" s="33">
         <v>8.42</v>
       </c>
-      <c r="F66" s="32">
+      <c r="F66" s="33">
         <v>8.72</v>
       </c>
-      <c r="G66" s="32">
+      <c r="G66" s="33">
         <v>8.78</v>
       </c>
-      <c r="H66" s="32">
+      <c r="H66" s="33">
         <v>8.47</v>
       </c>
-      <c r="I66" s="32">
+      <c r="I66" s="33">
         <v>8.46</v>
       </c>
-      <c r="J66" s="32">
+      <c r="J66" s="33">
         <v>7.69</v>
       </c>
-      <c r="K66" s="32">
+      <c r="K66" s="33">
         <v>6.87</v>
       </c>
-      <c r="L66" s="32">
+      <c r="L66" s="33">
         <v>6.61</v>
       </c>
-      <c r="M66" s="32">
+      <c r="M66" s="33">
         <v>6.6</v>
       </c>
-      <c r="N66" s="32">
+      <c r="N66" s="33">
         <v>6.09</v>
       </c>
-      <c r="O66" s="32">
+      <c r="O66" s="33">
         <v>6.96</v>
       </c>
-      <c r="P66" s="32">
+      <c r="P66" s="33">
         <v>7.96</v>
       </c>
-      <c r="Q66" s="32">
+      <c r="Q66" s="33">
         <v>8.31</v>
       </c>
-      <c r="R66" s="32">
+      <c r="R66" s="33">
         <v>8.29</v>
       </c>
-      <c r="S66" s="32">
+      <c r="S66" s="33">
         <v>8.88</v>
       </c>
-      <c r="T66" s="32">
+      <c r="T66" s="33">
         <v>7.85</v>
       </c>
-      <c r="U66" s="32">
+      <c r="U66" s="33">
         <v>7.0</v>
       </c>
-      <c r="V66" s="31"/>
-      <c r="W66" s="31"/>
-      <c r="X66" s="31"/>
-      <c r="Y66" s="31"/>
-      <c r="Z66" s="31"/>
-      <c r="AA66" s="31"/>
-      <c r="AB66" s="31"/>
-      <c r="AC66" s="31"/>
-      <c r="AD66" s="31"/>
+      <c r="V66" s="32"/>
+      <c r="W66" s="32"/>
+      <c r="X66" s="32"/>
+      <c r="Y66" s="32"/>
+      <c r="Z66" s="32"/>
+      <c r="AA66" s="32"/>
+      <c r="AB66" s="32"/>
+      <c r="AC66" s="32"/>
+      <c r="AD66" s="32"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="27" t="s">
-        <v>543</v>
-      </c>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28"/>
-      <c r="J67" s="28"/>
-      <c r="K67" s="28"/>
-      <c r="L67" s="28"/>
-      <c r="M67" s="28"/>
-      <c r="N67" s="28"/>
-      <c r="O67" s="28"/>
-      <c r="P67" s="28"/>
-      <c r="Q67" s="28"/>
-      <c r="R67" s="28"/>
-      <c r="S67" s="28"/>
-      <c r="T67" s="28"/>
-      <c r="U67" s="28"/>
-      <c r="V67" s="28"/>
-      <c r="W67" s="28"/>
-      <c r="X67" s="28"/>
-      <c r="Y67" s="28"/>
-      <c r="Z67" s="28"/>
-      <c r="AA67" s="28"/>
-      <c r="AB67" s="28"/>
-      <c r="AC67" s="28"/>
-      <c r="AD67" s="28"/>
+      <c r="A67" s="28" t="s">
+        <v>544</v>
+      </c>
+      <c r="B67" s="29"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="29"/>
+      <c r="E67" s="29"/>
+      <c r="F67" s="29"/>
+      <c r="G67" s="29"/>
+      <c r="H67" s="29"/>
+      <c r="I67" s="29"/>
+      <c r="J67" s="29"/>
+      <c r="K67" s="29"/>
+      <c r="L67" s="29"/>
+      <c r="M67" s="29"/>
+      <c r="N67" s="29"/>
+      <c r="O67" s="29"/>
+      <c r="P67" s="29"/>
+      <c r="Q67" s="29"/>
+      <c r="R67" s="29"/>
+      <c r="S67" s="29"/>
+      <c r="T67" s="29"/>
+      <c r="U67" s="29"/>
+      <c r="V67" s="29"/>
+      <c r="W67" s="29"/>
+      <c r="X67" s="29"/>
+      <c r="Y67" s="29"/>
+      <c r="Z67" s="29"/>
+      <c r="AA67" s="29"/>
+      <c r="AB67" s="29"/>
+      <c r="AC67" s="29"/>
+      <c r="AD67" s="29"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="29" t="s">
-        <v>544</v>
-      </c>
-      <c r="B68" s="32">
+      <c r="A68" s="30" t="s">
+        <v>545</v>
+      </c>
+      <c r="B68" s="33">
         <v>2.68</v>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="33">
         <v>2.64</v>
       </c>
-      <c r="D68" s="32">
+      <c r="D68" s="33">
         <v>3.64</v>
       </c>
-      <c r="E68" s="32">
+      <c r="E68" s="33">
         <v>10.5</v>
       </c>
-      <c r="F68" s="32">
+      <c r="F68" s="33">
         <v>8.68</v>
       </c>
-      <c r="G68" s="32">
+      <c r="G68" s="33">
         <v>7.9</v>
       </c>
-      <c r="H68" s="32">
+      <c r="H68" s="33">
         <v>7.53</v>
       </c>
-      <c r="I68" s="32">
+      <c r="I68" s="33">
         <v>13.25</v>
       </c>
-      <c r="J68" s="32">
+      <c r="J68" s="33">
         <v>10.26</v>
       </c>
-      <c r="K68" s="32">
+      <c r="K68" s="33">
         <v>8.3</v>
       </c>
-      <c r="L68" s="32">
+      <c r="L68" s="33">
         <v>8.04</v>
       </c>
-      <c r="M68" s="32">
+      <c r="M68" s="33">
         <v>7.58</v>
       </c>
-      <c r="N68" s="32">
+      <c r="N68" s="33">
         <v>6.33</v>
       </c>
-      <c r="O68" s="32">
+      <c r="O68" s="33">
         <v>7.1</v>
       </c>
-      <c r="P68" s="32">
+      <c r="P68" s="33">
         <v>9.83</v>
       </c>
-      <c r="Q68" s="32">
+      <c r="Q68" s="33">
         <v>10.2</v>
       </c>
-      <c r="R68" s="32">
+      <c r="R68" s="33">
         <v>7.17</v>
       </c>
-      <c r="S68" s="32">
+      <c r="S68" s="33">
         <v>15.86</v>
       </c>
-      <c r="T68" s="32">
+      <c r="T68" s="33">
         <v>11.28</v>
       </c>
-      <c r="U68" s="32">
+      <c r="U68" s="33">
         <v>12.13</v>
       </c>
-      <c r="V68" s="32">
+      <c r="V68" s="33">
         <v>10.62</v>
       </c>
-      <c r="W68" s="32">
+      <c r="W68" s="33">
         <v>9.75</v>
       </c>
-      <c r="X68" s="32">
+      <c r="X68" s="33">
         <v>7.02</v>
       </c>
-      <c r="Y68" s="32">
+      <c r="Y68" s="33">
         <v>8.08</v>
       </c>
-      <c r="Z68" s="32">
+      <c r="Z68" s="33">
         <v>7.06</v>
       </c>
-      <c r="AA68" s="32">
+      <c r="AA68" s="33">
         <v>6.02</v>
       </c>
-      <c r="AB68" s="32">
+      <c r="AB68" s="33">
         <v>3.02</v>
       </c>
-      <c r="AC68" s="32">
+      <c r="AC68" s="33">
         <v>2.57</v>
       </c>
-      <c r="AD68" s="32">
+      <c r="AD68" s="33">
         <v>0.43</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="29" t="s">
-        <v>545</v>
-      </c>
-      <c r="B69" s="32">
+      <c r="A69" s="30" t="s">
+        <v>546</v>
+      </c>
+      <c r="B69" s="33">
         <v>5.39</v>
       </c>
-      <c r="C69" s="32">
+      <c r="C69" s="33">
         <v>6.52</v>
       </c>
-      <c r="D69" s="32">
+      <c r="D69" s="33">
         <v>7.64</v>
       </c>
-      <c r="E69" s="32">
+      <c r="E69" s="33">
         <v>9.25</v>
       </c>
-      <c r="F69" s="32">
+      <c r="F69" s="33">
         <v>9.24</v>
       </c>
-      <c r="G69" s="32">
+      <c r="G69" s="33">
         <v>9.14</v>
       </c>
-      <c r="H69" s="32">
+      <c r="H69" s="33">
         <v>9.22</v>
       </c>
-      <c r="I69" s="32">
+      <c r="I69" s="33">
         <v>9.24</v>
       </c>
-      <c r="J69" s="32">
+      <c r="J69" s="33">
         <v>8.08</v>
       </c>
-      <c r="K69" s="32">
+      <c r="K69" s="33">
         <v>7.49</v>
       </c>
-      <c r="L69" s="32">
+      <c r="L69" s="33">
         <v>7.69</v>
       </c>
-      <c r="M69" s="32">
+      <c r="M69" s="33">
         <v>8.07</v>
       </c>
-      <c r="N69" s="32">
+      <c r="N69" s="33">
         <v>8.01</v>
       </c>
-      <c r="O69" s="32">
+      <c r="O69" s="33">
         <v>9.74</v>
       </c>
-      <c r="P69" s="32">
+      <c r="P69" s="33">
         <v>10.67</v>
       </c>
-      <c r="Q69" s="32">
+      <c r="Q69" s="33">
         <v>11.07</v>
       </c>
-      <c r="R69" s="32">
+      <c r="R69" s="33">
         <v>11.19</v>
       </c>
-      <c r="S69" s="32">
+      <c r="S69" s="33">
         <v>11.98</v>
       </c>
-      <c r="T69" s="32">
+      <c r="T69" s="33">
         <v>10.34</v>
       </c>
-      <c r="U69" s="32">
+      <c r="U69" s="33">
         <v>9.64</v>
       </c>
-      <c r="V69" s="32">
+      <c r="V69" s="33">
         <v>8.52</v>
       </c>
-      <c r="W69" s="32">
+      <c r="W69" s="33">
         <v>7.48</v>
       </c>
-      <c r="X69" s="32">
+      <c r="X69" s="33">
         <v>6.29</v>
       </c>
-      <c r="Y69" s="32">
+      <c r="Y69" s="33">
         <v>5.49</v>
       </c>
-      <c r="Z69" s="32">
+      <c r="Z69" s="33">
         <v>4.18</v>
       </c>
-      <c r="AA69" s="31"/>
-      <c r="AB69" s="31"/>
-      <c r="AC69" s="31"/>
-      <c r="AD69" s="31"/>
+      <c r="AA69" s="32"/>
+      <c r="AB69" s="32"/>
+      <c r="AC69" s="32"/>
+      <c r="AD69" s="32"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="27" t="s">
-        <v>546</v>
-      </c>
-      <c r="B70" s="28"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="28"/>
-      <c r="J70" s="28"/>
-      <c r="K70" s="28"/>
-      <c r="L70" s="28"/>
-      <c r="M70" s="28"/>
-      <c r="N70" s="28"/>
-      <c r="O70" s="28"/>
-      <c r="P70" s="28"/>
-      <c r="Q70" s="28"/>
-      <c r="R70" s="28"/>
-      <c r="S70" s="28"/>
-      <c r="T70" s="28"/>
-      <c r="U70" s="28"/>
-      <c r="V70" s="28"/>
-      <c r="W70" s="28"/>
-      <c r="X70" s="28"/>
-      <c r="Y70" s="28"/>
-      <c r="Z70" s="28"/>
-      <c r="AA70" s="28"/>
-      <c r="AB70" s="28"/>
-      <c r="AC70" s="28"/>
-      <c r="AD70" s="28"/>
+      <c r="A70" s="28" t="s">
+        <v>547</v>
+      </c>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="29"/>
+      <c r="E70" s="29"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="29"/>
+      <c r="I70" s="29"/>
+      <c r="J70" s="29"/>
+      <c r="K70" s="29"/>
+      <c r="L70" s="29"/>
+      <c r="M70" s="29"/>
+      <c r="N70" s="29"/>
+      <c r="O70" s="29"/>
+      <c r="P70" s="29"/>
+      <c r="Q70" s="29"/>
+      <c r="R70" s="29"/>
+      <c r="S70" s="29"/>
+      <c r="T70" s="29"/>
+      <c r="U70" s="29"/>
+      <c r="V70" s="29"/>
+      <c r="W70" s="29"/>
+      <c r="X70" s="29"/>
+      <c r="Y70" s="29"/>
+      <c r="Z70" s="29"/>
+      <c r="AA70" s="29"/>
+      <c r="AB70" s="29"/>
+      <c r="AC70" s="29"/>
+      <c r="AD70" s="29"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="29" t="s">
-        <v>547</v>
-      </c>
-      <c r="B71" s="32">
+      <c r="A71" s="30" t="s">
+        <v>548</v>
+      </c>
+      <c r="B71" s="33">
         <v>5.5</v>
       </c>
-      <c r="C71" s="32">
+      <c r="C71" s="33">
         <v>5.08</v>
       </c>
-      <c r="D71" s="32">
+      <c r="D71" s="33">
         <v>6.88</v>
       </c>
-      <c r="E71" s="32">
+      <c r="E71" s="33">
         <v>29.55</v>
       </c>
-      <c r="F71" s="32">
+      <c r="F71" s="33">
         <v>18.97</v>
       </c>
-      <c r="G71" s="32">
+      <c r="G71" s="33">
         <v>13.12</v>
       </c>
-      <c r="H71" s="32">
+      <c r="H71" s="33">
         <v>11.1</v>
       </c>
-      <c r="I71" s="32">
+      <c r="I71" s="33">
         <v>22.55</v>
       </c>
-      <c r="J71" s="32">
+      <c r="J71" s="33">
         <v>18.44</v>
       </c>
-      <c r="K71" s="32">
+      <c r="K71" s="33">
         <v>14.27</v>
       </c>
-      <c r="L71" s="32">
+      <c r="L71" s="33">
         <v>14.06</v>
       </c>
-      <c r="M71" s="32">
+      <c r="M71" s="33">
         <v>11.23</v>
       </c>
-      <c r="N71" s="32">
+      <c r="N71" s="33">
         <v>12.79</v>
       </c>
-      <c r="O71" s="32">
+      <c r="O71" s="33">
         <v>18.26</v>
       </c>
-      <c r="P71" s="32">
+      <c r="P71" s="33">
         <v>22.56</v>
       </c>
-      <c r="Q71" s="32">
+      <c r="Q71" s="33">
         <v>28.79</v>
       </c>
-      <c r="R71" s="31"/>
-      <c r="S71" s="30">
+      <c r="R71" s="32"/>
+      <c r="S71" s="31">
         <v>138.97</v>
       </c>
-      <c r="T71" s="31"/>
-      <c r="U71" s="32">
+      <c r="T71" s="32"/>
+      <c r="U71" s="33">
         <v>67.48</v>
       </c>
-      <c r="V71" s="32">
+      <c r="V71" s="33">
         <v>28.15</v>
       </c>
-      <c r="W71" s="32">
+      <c r="W71" s="33">
         <v>25.9</v>
       </c>
-      <c r="X71" s="32">
+      <c r="X71" s="33">
         <v>15.46</v>
       </c>
-      <c r="Y71" s="32">
+      <c r="Y71" s="33">
         <v>12.64</v>
       </c>
-      <c r="Z71" s="32">
+      <c r="Z71" s="33">
         <v>12.84</v>
       </c>
-      <c r="AA71" s="32">
+      <c r="AA71" s="33">
         <v>9.69</v>
       </c>
-      <c r="AB71" s="32">
+      <c r="AB71" s="33">
         <v>13.91</v>
       </c>
-      <c r="AC71" s="32">
+      <c r="AC71" s="33">
         <v>7.77</v>
       </c>
-      <c r="AD71" s="32">
+      <c r="AD71" s="33">
         <v>0.82</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="29" t="s">
-        <v>548</v>
-      </c>
-      <c r="B72" s="32">
+      <c r="A72" s="30" t="s">
+        <v>549</v>
+      </c>
+      <c r="B72" s="33">
         <v>11.36</v>
       </c>
-      <c r="C72" s="32">
+      <c r="C72" s="33">
         <v>13.01</v>
       </c>
-      <c r="D72" s="32">
+      <c r="D72" s="33">
         <v>14.25</v>
       </c>
-      <c r="E72" s="32">
+      <c r="E72" s="33">
         <v>16.94</v>
       </c>
-      <c r="F72" s="32">
+      <c r="F72" s="33">
         <v>15.96</v>
       </c>
-      <c r="G72" s="32">
+      <c r="G72" s="33">
         <v>15.15</v>
       </c>
-      <c r="H72" s="32">
+      <c r="H72" s="33">
         <v>15.43</v>
       </c>
-      <c r="I72" s="32">
+      <c r="I72" s="33">
         <v>15.51</v>
       </c>
-      <c r="J72" s="32">
+      <c r="J72" s="33">
         <v>13.98</v>
       </c>
-      <c r="K72" s="32">
+      <c r="K72" s="33">
         <v>13.69</v>
       </c>
-      <c r="L72" s="32">
+      <c r="L72" s="33">
         <v>14.77</v>
       </c>
-      <c r="M72" s="32">
+      <c r="M72" s="33">
         <v>16.79</v>
       </c>
-      <c r="N72" s="32">
+      <c r="N72" s="33">
         <v>25.2</v>
       </c>
-      <c r="O72" s="32">
+      <c r="O72" s="33">
         <v>40.48</v>
       </c>
-      <c r="P72" s="32">
+      <c r="P72" s="33">
         <v>95.5</v>
       </c>
-      <c r="Q72" s="30">
+      <c r="Q72" s="31">
         <v>198.02</v>
       </c>
-      <c r="R72" s="30">
+      <c r="R72" s="31">
         <v>269.23</v>
       </c>
-      <c r="S72" s="32">
+      <c r="S72" s="33">
         <v>86.63</v>
       </c>
-      <c r="T72" s="32">
+      <c r="T72" s="33">
         <v>53.0</v>
       </c>
-      <c r="U72" s="32">
+      <c r="U72" s="33">
         <v>24.38</v>
       </c>
-      <c r="V72" s="32">
+      <c r="V72" s="33">
         <v>17.87</v>
       </c>
-      <c r="W72" s="32">
+      <c r="W72" s="33">
         <v>14.03</v>
       </c>
-      <c r="X72" s="32">
+      <c r="X72" s="33">
         <v>12.27</v>
       </c>
-      <c r="Y72" s="32">
+      <c r="Y72" s="33">
         <v>11.2</v>
       </c>
-      <c r="Z72" s="32">
+      <c r="Z72" s="33">
         <v>8.89</v>
       </c>
-      <c r="AA72" s="31"/>
-      <c r="AB72" s="31"/>
-      <c r="AC72" s="31"/>
-      <c r="AD72" s="31"/>
+      <c r="AA72" s="32"/>
+      <c r="AB72" s="32"/>
+      <c r="AC72" s="32"/>
+      <c r="AD72" s="32"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>

--- a/data/hex_xlsx/LUOTEA.HE.xlsx
+++ b/data/hex_xlsx/LUOTEA.HE.xlsx
@@ -17847,7 +17847,9 @@
       <c r="T131" s="15">
         <v>123.32</v>
       </c>
-      <c r="U131" s="18"/>
+      <c r="U131" s="15">
+        <v>149.95</v>
+      </c>
       <c r="V131" s="19">
         <v>65.87</v>
       </c>

--- a/data/hex_xlsx/LUOTEA.HE.xlsx
+++ b/data/hex_xlsx/LUOTEA.HE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="551">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -1099,6 +1099,9 @@
   </si>
   <si>
     <t>Current liabilities</t>
+  </si>
+  <si>
+    <t>Bonds LT</t>
   </si>
   <si>
     <t>Reported Total Long Term Debt - Borrowings - Balancing value</t>
@@ -18838,8 +18841,8 @@
       <c r="W149" s="18"/>
     </row>
     <row r="150" ht="15.0" customHeight="1">
-      <c r="A150" s="14" t="s">
-        <v>339</v>
+      <c r="A150" s="27" t="s">
+        <v>360</v>
       </c>
       <c r="B150" s="18"/>
       <c r="C150" s="15">
@@ -18882,7 +18885,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B151" s="18"/>
       <c r="C151" s="18"/>
@@ -18911,7 +18914,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B152" s="19">
         <v>59.07</v>
@@ -18974,7 +18977,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B153" s="15">
         <v>103.96</v>
@@ -19035,7 +19038,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B154" s="18">
         <v>0.0</v>
@@ -19106,7 +19109,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B155" s="18"/>
       <c r="C155" s="19">
@@ -19159,7 +19162,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B156" s="18"/>
       <c r="C156" s="19">
@@ -19247,7 +19250,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B158" s="18"/>
       <c r="C158" s="18"/>
@@ -19280,7 +19283,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B159" s="18"/>
       <c r="C159" s="18"/>
@@ -19309,7 +19312,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B160" s="19">
         <v>10.63</v>
@@ -19451,7 +19454,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B162" s="19">
         <v>53.16</v>
@@ -19522,7 +19525,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B163" s="18"/>
       <c r="C163" s="18"/>
@@ -19563,7 +19566,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="16" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B164" s="17">
         <v>226.83</v>
@@ -19634,7 +19637,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B165" s="18"/>
       <c r="C165" s="18"/>
@@ -19665,7 +19668,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B166" s="19">
         <v>1.18</v>
@@ -19712,7 +19715,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="16" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B167" s="17">
         <v>1192.03</v>
@@ -19783,7 +19786,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B168" s="19">
         <v>11.81</v>
@@ -19854,7 +19857,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B169" s="18"/>
       <c r="C169" s="22">
@@ -19921,7 +19924,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B170" s="18"/>
       <c r="C170" s="18"/>
@@ -20011,7 +20014,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B172" s="18"/>
       <c r="C172" s="18"/>
@@ -20042,7 +20045,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B173" s="18"/>
       <c r="C173" s="18"/>
@@ -20144,7 +20147,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B175" s="19">
         <v>1.18</v>
@@ -20201,7 +20204,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B176" s="15">
         <v>609.6</v>
@@ -20272,7 +20275,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B177" s="18"/>
       <c r="C177" s="18"/>
@@ -20329,7 +20332,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B178" s="18"/>
       <c r="C178" s="18"/>
@@ -20366,7 +20369,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="16" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B179" s="17">
         <v>485.56</v>
@@ -20498,7 +20501,7 @@
     </row>
     <row r="181" ht="15.0" customHeight="1">
       <c r="A181" s="16" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B181" s="20"/>
       <c r="C181" s="20"/>
@@ -20559,7 +20562,7 @@
     </row>
     <row r="182" ht="15.0" customHeight="1">
       <c r="A182" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B182" s="18"/>
       <c r="C182" s="18"/>
@@ -20592,7 +20595,7 @@
     </row>
     <row r="183" ht="15.0" customHeight="1">
       <c r="A183" s="16" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B183" s="17">
         <v>485.56</v>
@@ -20663,7 +20666,7 @@
     </row>
     <row r="184" ht="15.0" customHeight="1">
       <c r="A184" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B184" s="18"/>
       <c r="C184" s="18"/>
@@ -20702,7 +20705,7 @@
     </row>
     <row r="185" ht="15.0" customHeight="1">
       <c r="A185" s="16" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B185" s="17">
         <v>1677.59</v>
@@ -20773,7 +20776,7 @@
     </row>
     <row r="186" ht="15.0" customHeight="1">
       <c r="A186" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B186" s="19">
         <v>38.21</v>
@@ -20844,7 +20847,7 @@
     </row>
     <row r="187" ht="15.0" customHeight="1">
       <c r="A187" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B187" s="19">
         <v>0.59</v>
@@ -20915,7 +20918,7 @@
     </row>
     <row r="188" ht="15.0" customHeight="1">
       <c r="A188" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B188" s="19">
         <v>38.8</v>
@@ -20986,7 +20989,7 @@
     </row>
     <row r="189" ht="15.0" customHeight="1">
       <c r="A189" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B189" s="18"/>
       <c r="C189" s="15">
@@ -21051,7 +21054,7 @@
     </row>
     <row r="190" ht="15.0" customHeight="1">
       <c r="A190" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B190" s="18"/>
       <c r="C190" s="19">
@@ -21116,7 +21119,7 @@
     </row>
     <row r="191" ht="15.0" customHeight="1">
       <c r="A191" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B191" s="18"/>
       <c r="C191" s="15">
@@ -21181,7 +21184,7 @@
     </row>
     <row r="192" ht="15.0" customHeight="1">
       <c r="A192" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B192" s="18"/>
       <c r="C192" s="19">
@@ -21246,7 +21249,7 @@
     </row>
     <row r="193" ht="15.0" customHeight="1">
       <c r="A193" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B193" s="18"/>
       <c r="C193" s="15">
@@ -21311,7 +21314,7 @@
     </row>
     <row r="194" ht="15.0" customHeight="1">
       <c r="A194" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B194" s="18"/>
       <c r="C194" s="18">
@@ -21374,7 +21377,7 @@
     </row>
     <row r="195" ht="15.0" customHeight="1">
       <c r="A195" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B195" s="18"/>
       <c r="C195" s="18">
@@ -21433,7 +21436,7 @@
     </row>
     <row r="196" ht="15.0" customHeight="1">
       <c r="A196" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B196" s="18"/>
       <c r="C196" s="18"/>
@@ -21470,7 +21473,7 @@
     </row>
     <row r="197" ht="15.0" customHeight="1">
       <c r="A197" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B197" s="18"/>
       <c r="C197" s="18"/>
@@ -21511,7 +21514,7 @@
     </row>
     <row r="198" ht="15.0" customHeight="1">
       <c r="A198" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B198" s="18"/>
       <c r="C198" s="18"/>
@@ -21573,7 +21576,7 @@
     </row>
     <row r="200" ht="15.0" customHeight="1">
       <c r="A200" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B200" s="18"/>
       <c r="C200" s="18"/>
@@ -21653,7 +21656,7 @@
     </row>
     <row r="202" ht="15.0" customHeight="1">
       <c r="A202" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B202" s="18"/>
       <c r="C202" s="18"/>
@@ -21694,7 +21697,7 @@
     </row>
     <row r="203" ht="15.0" customHeight="1">
       <c r="A203" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B203" s="18"/>
       <c r="C203" s="18"/>
@@ -21735,7 +21738,7 @@
     </row>
     <row r="204" ht="15.0" customHeight="1">
       <c r="A204" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B204" s="18"/>
       <c r="C204" s="18"/>
@@ -21770,7 +21773,7 @@
     </row>
     <row r="205" ht="15.0" customHeight="1">
       <c r="A205" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B205" s="18"/>
       <c r="C205" s="18"/>
@@ -21799,7 +21802,7 @@
     </row>
     <row r="206" ht="15.0" customHeight="1">
       <c r="A206" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B206" s="18"/>
       <c r="C206" s="18"/>
@@ -21834,7 +21837,7 @@
     </row>
     <row r="207" ht="15.0" customHeight="1">
       <c r="A207" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B207" s="18"/>
       <c r="C207" s="18"/>
@@ -21871,7 +21874,7 @@
     </row>
     <row r="208" ht="15.0" customHeight="1">
       <c r="A208" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B208" s="18"/>
       <c r="C208" s="15">
@@ -21926,7 +21929,7 @@
     </row>
     <row r="209" ht="15.0" customHeight="1">
       <c r="A209" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B209" s="18"/>
       <c r="C209" s="15">
@@ -21981,7 +21984,7 @@
     </row>
     <row r="210" ht="15.0" customHeight="1">
       <c r="A210" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B210" s="18"/>
       <c r="C210" s="15">
@@ -22036,7 +22039,7 @@
     </row>
     <row r="211" ht="15.0" customHeight="1">
       <c r="A211" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B211" s="18"/>
       <c r="C211" s="19">
@@ -22091,7 +22094,7 @@
     </row>
     <row r="212" ht="15.0" customHeight="1">
       <c r="A212" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B212" s="18"/>
       <c r="C212" s="19">
@@ -22144,7 +22147,7 @@
     </row>
     <row r="213" ht="15.0" customHeight="1">
       <c r="A213" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B213" s="18"/>
       <c r="C213" s="19">
@@ -22195,7 +22198,7 @@
     </row>
     <row r="214" ht="15.0" customHeight="1">
       <c r="A214" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B214" s="18"/>
       <c r="C214" s="15">
@@ -22246,7 +22249,7 @@
     </row>
     <row r="215" ht="15.0" customHeight="1">
       <c r="A215" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B215" s="18"/>
       <c r="C215" s="18"/>
@@ -22277,7 +22280,7 @@
     </row>
     <row r="216" ht="15.0" customHeight="1">
       <c r="A216" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B216" s="18"/>
       <c r="C216" s="18"/>
@@ -22308,7 +22311,7 @@
     </row>
     <row r="217" ht="15.0" customHeight="1">
       <c r="A217" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B217" s="18"/>
       <c r="C217" s="18"/>
@@ -22343,7 +22346,7 @@
     </row>
     <row r="218" ht="15.0" customHeight="1">
       <c r="A218" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B218" s="18"/>
       <c r="C218" s="18"/>
@@ -22372,7 +22375,7 @@
     </row>
     <row r="219" ht="15.0" customHeight="1">
       <c r="A219" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B219" s="18"/>
       <c r="C219" s="18"/>
@@ -22407,7 +22410,7 @@
     </row>
     <row r="220" ht="15.0" customHeight="1">
       <c r="A220" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B220" s="19">
         <v>38.21</v>
@@ -22478,7 +22481,7 @@
     </row>
     <row r="221" ht="15.0" customHeight="1">
       <c r="A221" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B221" s="19">
         <v>0.59</v>
@@ -22549,7 +22552,7 @@
     </row>
     <row r="222" ht="15.0" customHeight="1">
       <c r="A222" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B222" s="19">
         <v>38.8</v>
@@ -22620,7 +22623,7 @@
     </row>
     <row r="223" ht="15.0" customHeight="1">
       <c r="A223" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B223" s="19">
         <v>1.0</v>
@@ -23487,7 +23490,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23873,70 +23876,70 @@
         <v>44</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -24012,7 +24015,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -24110,7 +24113,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B20" s="21">
         <v>-7.02</v>
@@ -24145,7 +24148,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B21" s="21">
         <v>-22.23</v>
@@ -24182,7 +24185,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -24219,7 +24222,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -24252,7 +24255,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B24" s="21">
         <v>-44.47</v>
@@ -24283,7 +24286,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B25" s="22">
         <v>-1565.8</v>
@@ -24312,7 +24315,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B26" s="15">
         <v>1069.62</v>
@@ -24438,7 +24441,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -24554,7 +24557,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B30" s="15">
         <v>623.75</v>
@@ -24688,7 +24691,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
@@ -24733,7 +24736,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B33" s="18"/>
       <c r="C33" s="18"/>
@@ -24764,7 +24767,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
@@ -24819,7 +24822,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B35" s="19">
         <v>10.53</v>
@@ -24886,7 +24889,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
@@ -24917,7 +24920,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B37" s="18"/>
       <c r="C37" s="18"/>
@@ -24946,7 +24949,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B38" s="21">
         <v>-55.0</v>
@@ -25001,7 +25004,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B39" s="22">
         <v>-148.62</v>
@@ -25143,7 +25146,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B41" s="19">
         <v>95.96</v>
@@ -25214,7 +25217,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B42" s="18"/>
       <c r="C42" s="18"/>
@@ -25247,7 +25250,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B43" s="18"/>
       <c r="C43" s="18"/>
@@ -25280,7 +25283,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B44" s="22">
         <v>-124.05</v>
@@ -25351,7 +25354,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B45" s="19">
         <v>7.02</v>
@@ -25422,7 +25425,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B46" s="21">
         <v>-12.87</v>
@@ -25493,7 +25496,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B47" s="19">
         <v>1.17</v>
@@ -25536,7 +25539,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="16" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B48" s="17">
         <v>884.71</v>
@@ -25607,7 +25610,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B49" s="22">
         <v>-129.9</v>
@@ -25678,7 +25681,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
@@ -25725,7 +25728,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
@@ -25756,7 +25759,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B52" s="22">
         <v>-273.84</v>
@@ -25827,7 +25830,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
@@ -25876,7 +25879,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B54" s="19">
         <v>17.55</v>
@@ -25925,7 +25928,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B55" s="18"/>
       <c r="C55" s="18"/>
@@ -25978,7 +25981,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
@@ -26043,7 +26046,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B57" s="19">
         <v>18.72</v>
@@ -26100,7 +26103,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
@@ -26131,7 +26134,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
@@ -26172,7 +26175,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
@@ -26205,7 +26208,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
@@ -26236,7 +26239,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
@@ -26271,7 +26274,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="16" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B63" s="25">
         <v>-367.46</v>
@@ -26342,7 +26345,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B64" s="15">
         <v>351.08</v>
@@ -26407,7 +26410,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B65" s="22">
         <v>-351.08</v>
@@ -26444,7 +26447,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B66" s="15">
         <v>643.64</v>
@@ -26515,7 +26518,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
@@ -26544,7 +26547,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B68" s="22">
         <v>-478.64</v>
@@ -26613,7 +26616,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B69" s="22">
         <v>-223.52</v>
@@ -26684,7 +26687,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B70" s="22">
         <v>-236.39</v>
@@ -26727,7 +26730,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B71" s="18"/>
       <c r="C71" s="18"/>
@@ -26774,7 +26777,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B72" s="18"/>
       <c r="C72" s="18"/>
@@ -26803,7 +26806,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B73" s="18"/>
       <c r="C73" s="18"/>
@@ -26832,7 +26835,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B74" s="18"/>
       <c r="C74" s="18"/>
@@ -26871,7 +26874,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B75" s="18"/>
       <c r="C75" s="18"/>
@@ -26902,7 +26905,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
@@ -26935,7 +26938,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="16" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B77" s="25">
         <v>-294.9</v>
@@ -27006,7 +27009,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B78" s="19">
         <v>1.17</v>
@@ -27077,7 +27080,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B79" s="15">
         <v>400.49</v>
@@ -27148,7 +27151,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B80" s="15">
         <v>185.48</v>
@@ -27219,7 +27222,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B81" s="15">
         <v>222.35</v>
@@ -27274,7 +27277,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B82" s="22">
         <v>-437.68</v>
@@ -27303,7 +27306,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="16" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B83" s="25">
         <v>-214.16</v>
@@ -27374,7 +27377,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B84" s="18"/>
       <c r="C84" s="18"/>
@@ -27403,7 +27406,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B85" s="18"/>
       <c r="C85" s="18"/>
@@ -28366,7 +28369,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -28538,28 +28541,28 @@
         <v>39</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -29020,7 +29023,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -29120,33 +29123,33 @@
         <v>71</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="28" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
@@ -29180,7 +29183,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="30" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B21" s="31">
         <v>2619.09</v>
@@ -29272,7 +29275,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="30" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B22" s="31">
         <v>5038.52</v>
@@ -29356,7 +29359,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="28" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B23" s="29"/>
       <c r="C23" s="29"/>
@@ -29390,7 +29393,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="30" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B24" s="31">
         <v>818.75</v>
@@ -29482,7 +29485,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="30" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B25" s="31">
         <v>3191.34</v>
@@ -29566,7 +29569,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="28" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B26" s="29"/>
       <c r="C26" s="29"/>
@@ -29600,7 +29603,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="30" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B27" s="33">
         <v>21.1</v>
@@ -29692,7 +29695,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="30" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B28" s="33">
         <v>30.47</v>
@@ -29776,7 +29779,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="28" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
@@ -29810,7 +29813,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="30" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B30" s="34">
         <v>59.17</v>
@@ -29902,7 +29905,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="30" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B31" s="34">
         <v>38.12</v>
@@ -29986,7 +29989,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="28" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
@@ -30020,7 +30023,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="30" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B33" s="34">
         <v>27.32</v>
@@ -30110,7 +30113,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="30" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B34" s="34">
         <v>21.17</v>
@@ -30184,7 +30187,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="30" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B35" s="34">
         <v>27.32</v>
@@ -30276,7 +30279,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="30" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B36" s="34">
         <v>21.17</v>
@@ -30360,7 +30363,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="28" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
@@ -30394,7 +30397,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="30" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B38" s="33">
         <v>0.33</v>
@@ -30486,7 +30489,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="30" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B39" s="33">
         <v>0.46</v>
@@ -30570,7 +30573,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="28" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B40" s="29"/>
       <c r="C40" s="29"/>
@@ -30604,7 +30607,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="30" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B41" s="33">
         <v>6.85</v>
@@ -30690,7 +30693,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="30" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B42" s="33">
         <v>11.79</v>
@@ -30768,7 +30771,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="28" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B43" s="29"/>
       <c r="C43" s="29"/>
@@ -30802,7 +30805,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="30" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B44" s="33">
         <v>0.09</v>
@@ -30894,7 +30897,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="30" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B45" s="33">
         <v>0.12</v>
@@ -30978,7 +30981,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="28" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
@@ -31012,7 +31015,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="30" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B47" s="33">
         <v>1.69</v>
@@ -31100,7 +31103,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="30" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B48" s="33">
         <v>2.62</v>
@@ -31184,7 +31187,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="28" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B49" s="29"/>
       <c r="C49" s="29"/>
@@ -31218,7 +31221,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="30" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B50" s="33">
         <v>1.26</v>
@@ -31310,7 +31313,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="30" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B51" s="33">
         <v>1.27</v>
@@ -31394,7 +31397,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="28" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B52" s="29"/>
       <c r="C52" s="29"/>
@@ -31428,7 +31431,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="30" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B53" s="32"/>
       <c r="C53" s="33">
@@ -31518,7 +31521,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="30" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B54" s="33">
         <v>4.39</v>
@@ -31602,7 +31605,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="28" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B55" s="29"/>
       <c r="C55" s="29"/>
@@ -31636,7 +31639,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="30" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B56" s="33">
         <v>2.49</v>
@@ -31728,7 +31731,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="30" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B57" s="33">
         <v>0.46</v>
@@ -31812,7 +31815,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="28" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B58" s="29"/>
       <c r="C58" s="29"/>
@@ -31846,7 +31849,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="30" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B59" s="32"/>
       <c r="C59" s="36">
@@ -31934,7 +31937,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="30" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B60" s="32"/>
       <c r="C60" s="36">
@@ -32014,7 +32017,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="28" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B61" s="29"/>
       <c r="C61" s="29"/>
@@ -32048,7 +32051,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="30" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B62" s="33">
         <v>0.29</v>
@@ -32140,7 +32143,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="30" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B63" s="33">
         <v>0.54</v>
@@ -32224,7 +32227,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="28" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B64" s="29"/>
       <c r="C64" s="29"/>
@@ -32258,7 +32261,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="30" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B65" s="33">
         <v>2.38</v>
@@ -32348,7 +32351,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="30" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B66" s="33">
         <v>4.67</v>
@@ -32422,7 +32425,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="28" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B67" s="29"/>
       <c r="C67" s="29"/>
@@ -32456,7 +32459,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="30" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B68" s="33">
         <v>2.68</v>
@@ -32548,7 +32551,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="30" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B69" s="33">
         <v>5.39</v>
@@ -32632,7 +32635,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="28" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B70" s="29"/>
       <c r="C70" s="29"/>
@@ -32666,7 +32669,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="30" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B71" s="33">
         <v>5.5</v>
@@ -32754,7 +32757,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="30" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B72" s="33">
         <v>11.36</v>
